--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -1371,7 +1371,7 @@
         <v>-3.2048</v>
       </c>
       <c r="I9">
-        <v>0.1313833333333334</v>
+        <v>0.1313833333333333</v>
       </c>
       <c r="J9">
         <v>6.5</v>
@@ -1827,7 +1827,7 @@
         <v>-7.6155</v>
       </c>
       <c r="I21">
-        <v>0.01529912280701757</v>
+        <v>0.01529912280701754</v>
       </c>
       <c r="J21">
         <v>6.5</v>
@@ -1865,7 +1865,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I22">
-        <v>0.1306789473684211</v>
+        <v>0.130678947368421</v>
       </c>
       <c r="J22">
         <v>6.5</v>
@@ -2017,7 +2017,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I26">
-        <v>-0.057259649122807</v>
+        <v>-0.05725964912280705</v>
       </c>
       <c r="J26">
         <v>6.5</v>
@@ -2055,7 +2055,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I27">
-        <v>-0.04229736842105262</v>
+        <v>-0.04229736842105265</v>
       </c>
       <c r="J27">
         <v>6.5</v>
@@ -2663,7 +2663,7 @@
         <v>-4.1055</v>
       </c>
       <c r="I43">
-        <v>0.4946271929824561</v>
+        <v>0.4946271929824562</v>
       </c>
       <c r="J43">
         <v>6.5</v>
@@ -2929,7 +2929,7 @@
         <v>-5.1686</v>
       </c>
       <c r="I50">
-        <v>0.0683140350877193</v>
+        <v>0.06831403508771929</v>
       </c>
       <c r="J50">
         <v>6.5</v>
@@ -3081,7 +3081,7 @@
         <v>-7.5421</v>
       </c>
       <c r="I54">
-        <v>-8.771929824540961E-06</v>
+        <v>-8.771929824509795E-06</v>
       </c>
       <c r="J54">
         <v>6.5</v>
@@ -3119,7 +3119,7 @@
         <v>-6.4654</v>
       </c>
       <c r="I55">
-        <v>0.5864333333333333</v>
+        <v>0.5864333333333334</v>
       </c>
       <c r="J55">
         <v>6.5</v>
@@ -3461,7 +3461,7 @@
         <v>-4.7353</v>
       </c>
       <c r="I64">
-        <v>0.7190307017543861</v>
+        <v>0.7190307017543859</v>
       </c>
       <c r="J64">
         <v>6.5</v>
@@ -3651,7 +3651,7 @@
         <v>-5.3978</v>
       </c>
       <c r="I69">
-        <v>0.700928947368421</v>
+        <v>0.7009289473684209</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3917,7 +3917,7 @@
         <v>-7.1749</v>
       </c>
       <c r="I76">
-        <v>0.3746035087719298</v>
+        <v>0.3746035087719299</v>
       </c>
       <c r="J76">
         <v>6.5</v>
@@ -4145,7 +4145,7 @@
         <v>-4.7122</v>
       </c>
       <c r="I82">
-        <v>1.56688947368421</v>
+        <v>1.566889473684211</v>
       </c>
       <c r="J82">
         <v>6.5</v>
@@ -4259,7 +4259,7 @@
         <v>-5.5616</v>
       </c>
       <c r="I85">
-        <v>-0.005708771929824558</v>
+        <v>-0.005708771929824544</v>
       </c>
       <c r="J85">
         <v>6.5</v>
@@ -4373,7 +4373,7 @@
         <v>-4.5504</v>
       </c>
       <c r="I88">
-        <v>0.8666499999999999</v>
+        <v>0.86665</v>
       </c>
       <c r="J88">
         <v>6.5</v>
@@ -4525,7 +4525,7 @@
         <v>-5.325</v>
       </c>
       <c r="I92">
-        <v>0.06181315789473682</v>
+        <v>0.06181315789473685</v>
       </c>
       <c r="J92">
         <v>6.5</v>
@@ -4563,7 +4563,7 @@
         <v>-5.5639</v>
       </c>
       <c r="I93">
-        <v>0.03160175438596489</v>
+        <v>0.03160175438596493</v>
       </c>
       <c r="J93">
         <v>6.5</v>
@@ -4601,7 +4601,7 @@
         <v>-4.9943</v>
       </c>
       <c r="I94">
-        <v>0.01033684210526314</v>
+        <v>0.01033684210526312</v>
       </c>
       <c r="J94">
         <v>6.5</v>
@@ -4639,7 +4639,7 @@
         <v>-5.2715</v>
       </c>
       <c r="I95">
-        <v>0.3232850877192982</v>
+        <v>0.3232850877192983</v>
       </c>
       <c r="J95">
         <v>6.5</v>
@@ -5019,7 +5019,7 @@
         <v>-5.7006</v>
       </c>
       <c r="I105">
-        <v>-0.2644166666666666</v>
+        <v>-0.2644166666666667</v>
       </c>
       <c r="J105">
         <v>6.5</v>
@@ -5057,7 +5057,7 @@
         <v>-3.7504</v>
       </c>
       <c r="I106">
-        <v>1.033949122807017</v>
+        <v>1.033949122807018</v>
       </c>
       <c r="J106">
         <v>6.5</v>
@@ -5209,7 +5209,7 @@
         <v>-7.6593</v>
       </c>
       <c r="I110">
-        <v>-0.304978947368421</v>
+        <v>-0.3049789473684211</v>
       </c>
       <c r="J110">
         <v>6.5</v>
@@ -5323,7 +5323,7 @@
         <v>-6.1612</v>
       </c>
       <c r="I113">
-        <v>0.1059350877192982</v>
+        <v>0.1059350877192983</v>
       </c>
       <c r="J113">
         <v>6.5</v>
@@ -5551,7 +5551,7 @@
         <v>-4.9268</v>
       </c>
       <c r="I119">
-        <v>0.1207350877192982</v>
+        <v>0.1207350877192983</v>
       </c>
       <c r="J119">
         <v>6.5</v>
@@ -5589,7 +5589,7 @@
         <v>-5.1558</v>
       </c>
       <c r="I120">
-        <v>-0.1938728070175438</v>
+        <v>-0.1938728070175439</v>
       </c>
       <c r="J120">
         <v>6.5</v>
@@ -5817,7 +5817,7 @@
         <v>-4.8548</v>
       </c>
       <c r="I126">
-        <v>-0.02022920353982302</v>
+        <v>-0.020229203539823</v>
       </c>
       <c r="J126">
         <v>6.5</v>
@@ -6045,7 +6045,7 @@
         <v>-4.7021</v>
       </c>
       <c r="I132">
-        <v>-0.04365350877192982</v>
+        <v>-0.04365350877192984</v>
       </c>
       <c r="J132">
         <v>6.5</v>
@@ -6121,7 +6121,7 @@
         <v>-5.4098</v>
       </c>
       <c r="I134">
-        <v>-0.2065377192982456</v>
+        <v>-0.2065377192982457</v>
       </c>
       <c r="J134">
         <v>6.5</v>
@@ -6235,7 +6235,7 @@
         <v>-6.3804</v>
       </c>
       <c r="I137">
-        <v>0.01184473684210528</v>
+        <v>0.01184473684210527</v>
       </c>
       <c r="J137">
         <v>6.5</v>
@@ -6273,7 +6273,7 @@
         <v>-6.1406</v>
       </c>
       <c r="I138">
-        <v>-0.1075850877192983</v>
+        <v>-0.1075850877192982</v>
       </c>
       <c r="J138">
         <v>6.5</v>
@@ -6501,7 +6501,7 @@
         <v>-4.9361</v>
       </c>
       <c r="I144">
-        <v>0.4951833333333334</v>
+        <v>0.4951833333333333</v>
       </c>
       <c r="J144">
         <v>6.5</v>
@@ -6653,7 +6653,7 @@
         <v>-4.2556</v>
       </c>
       <c r="I148">
-        <v>0.5377736842105264</v>
+        <v>0.5377736842105263</v>
       </c>
       <c r="J148">
         <v>6.5</v>
@@ -6767,7 +6767,7 @@
         <v>-5.5488</v>
       </c>
       <c r="I151">
-        <v>-0.09169736842105264</v>
+        <v>-0.09169736842105261</v>
       </c>
       <c r="J151">
         <v>6.5</v>
@@ -6805,7 +6805,7 @@
         <v>-4.8797</v>
       </c>
       <c r="I152">
-        <v>-0.2253307017543859</v>
+        <v>-0.225330701754386</v>
       </c>
       <c r="J152">
         <v>6.5</v>
@@ -7071,7 +7071,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I159">
-        <v>0.03470701754385961</v>
+        <v>0.03470701754385962</v>
       </c>
       <c r="J159">
         <v>6.5</v>
@@ -7299,7 +7299,7 @@
         <v>-4.6257</v>
       </c>
       <c r="I165">
-        <v>0.1766570175438597</v>
+        <v>0.1766570175438596</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7451,7 +7451,7 @@
         <v>-4.7737</v>
       </c>
       <c r="I169">
-        <v>0.2246771929824562</v>
+        <v>0.2246771929824561</v>
       </c>
       <c r="J169">
         <v>6.5</v>
@@ -7527,7 +7527,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I171">
-        <v>-0.04652807017543857</v>
+        <v>-0.04652807017543858</v>
       </c>
       <c r="J171">
         <v>6.5</v>
@@ -7831,7 +7831,7 @@
         <v>-8.343400000000001</v>
       </c>
       <c r="I179">
-        <v>-0.8040798245614036</v>
+        <v>-0.8040798245614035</v>
       </c>
       <c r="J179">
         <v>6.5</v>
@@ -8021,7 +8021,7 @@
         <v>-8.4955</v>
       </c>
       <c r="I184">
-        <v>0.5397631578947368</v>
+        <v>0.5397631578947369</v>
       </c>
       <c r="J184">
         <v>6.5</v>
@@ -8059,7 +8059,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I185">
-        <v>-0.008550000000000019</v>
+        <v>-0.008550000000000004</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -8173,7 +8173,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I188">
-        <v>-0.05237192982456141</v>
+        <v>-0.0523719298245614</v>
       </c>
       <c r="J188">
         <v>6.5</v>
@@ -8401,7 +8401,7 @@
         <v>-5.5309</v>
       </c>
       <c r="I194">
-        <v>-0.5048745614035087</v>
+        <v>-0.5048745614035088</v>
       </c>
       <c r="J194">
         <v>6.5</v>
@@ -8477,7 +8477,7 @@
         <v>-4.9463</v>
       </c>
       <c r="I196">
-        <v>0.1976649122807017</v>
+        <v>0.1976649122807018</v>
       </c>
       <c r="J196">
         <v>6.5</v>
@@ -8667,7 +8667,7 @@
         <v>-5.7729</v>
       </c>
       <c r="I201">
-        <v>0.2905122807017543</v>
+        <v>0.2905122807017544</v>
       </c>
       <c r="J201">
         <v>6.5</v>
@@ -8705,7 +8705,7 @@
         <v>-5.0406</v>
       </c>
       <c r="I202">
-        <v>-0.07873333333333332</v>
+        <v>-0.07873333333333334</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8743,7 +8743,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I203">
-        <v>1.477787719298245</v>
+        <v>1.477787719298246</v>
       </c>
       <c r="J203">
         <v>6.5</v>
@@ -8857,7 +8857,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I206">
-        <v>-0.006774561403508784</v>
+        <v>-0.006774561403508799</v>
       </c>
       <c r="J206">
         <v>6.5</v>
@@ -9351,7 +9351,7 @@
         <v>-6.7781</v>
       </c>
       <c r="I219">
-        <v>0.3909201754385965</v>
+        <v>0.3909201754385966</v>
       </c>
       <c r="J219">
         <v>6.5</v>
@@ -9959,7 +9959,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I235">
-        <v>-0.02176052631578942</v>
+        <v>-0.02176052631578948</v>
       </c>
       <c r="J235">
         <v>6.5</v>
@@ -10111,7 +10111,7 @@
         <v>-6.8644</v>
       </c>
       <c r="I239">
-        <v>-0.3149601769911505</v>
+        <v>-0.3149601769911504</v>
       </c>
       <c r="J239">
         <v>6.5</v>
@@ -10301,7 +10301,7 @@
         <v>-7.8256</v>
       </c>
       <c r="I244">
-        <v>0.038790350877193</v>
+        <v>0.03879035087719299</v>
       </c>
       <c r="J244">
         <v>6.5</v>
@@ -10833,7 +10833,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I258">
-        <v>0.03353596491228067</v>
+        <v>0.03353596491228068</v>
       </c>
       <c r="J258">
         <v>6.5</v>
@@ -10871,7 +10871,7 @@
         <v>-6.9585</v>
       </c>
       <c r="I259">
-        <v>-1.168720175438597</v>
+        <v>-1.168720175438596</v>
       </c>
       <c r="J259">
         <v>6.5</v>
@@ -11213,7 +11213,7 @@
         <v>-7.0616</v>
       </c>
       <c r="I268">
-        <v>0.3301157894736841</v>
+        <v>0.3301157894736843</v>
       </c>
       <c r="J268">
         <v>6.5</v>
@@ -11479,7 +11479,7 @@
         <v>-9.9345</v>
       </c>
       <c r="I275">
-        <v>-0.09859999999999999</v>
+        <v>-0.09860000000000003</v>
       </c>
       <c r="J275">
         <v>6.5</v>
@@ -11593,7 +11593,7 @@
         <v>-5.2084</v>
       </c>
       <c r="I278">
-        <v>0.4989368421052631</v>
+        <v>0.4989368421052632</v>
       </c>
       <c r="J278">
         <v>6.5</v>
@@ -11631,7 +11631,7 @@
         <v>-8.186500000000001</v>
       </c>
       <c r="I279">
-        <v>0.7274377192982455</v>
+        <v>0.7274377192982456</v>
       </c>
       <c r="J279">
         <v>6.5</v>
@@ -11821,7 +11821,7 @@
         <v>-5.579</v>
       </c>
       <c r="I284">
-        <v>0.03944473684210525</v>
+        <v>0.03944473684210527</v>
       </c>
       <c r="J284">
         <v>6.5</v>
@@ -12809,7 +12809,7 @@
         <v>-5.6215</v>
       </c>
       <c r="I310">
-        <v>0.9777149122807017</v>
+        <v>0.9777149122807018</v>
       </c>
       <c r="J310">
         <v>6.5</v>
@@ -13721,7 +13721,7 @@
         <v>-4.7487</v>
       </c>
       <c r="I334">
-        <v>-0.0171421052631579</v>
+        <v>-0.01714210526315786</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -13835,7 +13835,7 @@
         <v>-6.3764</v>
       </c>
       <c r="I337">
-        <v>0.8450508771929823</v>
+        <v>0.8450508771929826</v>
       </c>
       <c r="J337">
         <v>6.5</v>
@@ -14481,7 +14481,7 @@
         <v>-2.9022</v>
       </c>
       <c r="I354">
-        <v>1.770550877192982</v>
+        <v>1.770550877192983</v>
       </c>
       <c r="J354">
         <v>6.5</v>
@@ -14671,7 +14671,7 @@
         <v>-7.823</v>
       </c>
       <c r="I359">
-        <v>0.2566728070175439</v>
+        <v>0.2566728070175438</v>
       </c>
       <c r="J359">
         <v>6.5</v>
@@ -14785,7 +14785,7 @@
         <v>-5.1904</v>
       </c>
       <c r="I362">
-        <v>0.05131228070175439</v>
+        <v>0.05131228070175438</v>
       </c>
       <c r="J362">
         <v>6.5</v>
@@ -15393,7 +15393,7 @@
         <v>-5.1258</v>
       </c>
       <c r="I378">
-        <v>0.7531894736842104</v>
+        <v>0.7531894736842105</v>
       </c>
       <c r="J378">
         <v>6.5</v>
@@ -15431,7 +15431,7 @@
         <v>-6.8295</v>
       </c>
       <c r="I379">
-        <v>0.3240798245614035</v>
+        <v>0.3240798245614036</v>
       </c>
       <c r="J379">
         <v>6.5</v>
@@ -16343,7 +16343,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I403">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J403">
         <v>6.5</v>
@@ -16875,7 +16875,7 @@
         <v>-6.1057</v>
       </c>
       <c r="I417">
-        <v>0.7022105263157894</v>
+        <v>0.7022105263157895</v>
       </c>
       <c r="J417">
         <v>6.5</v>
@@ -17179,7 +17179,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I425">
-        <v>0.8890823008849558</v>
+        <v>0.8890823008849557</v>
       </c>
       <c r="J425">
         <v>6.5</v>
@@ -17445,7 +17445,7 @@
         <v>-7.3019</v>
       </c>
       <c r="I432">
-        <v>0.1687754385964912</v>
+        <v>0.1687754385964913</v>
       </c>
       <c r="J432">
         <v>6.5</v>
@@ -18243,7 +18243,7 @@
         <v>-5.4613</v>
       </c>
       <c r="I453">
-        <v>0.9106842105263158</v>
+        <v>0.9106842105263159</v>
       </c>
       <c r="J453">
         <v>6.5</v>
@@ -18319,7 +18319,7 @@
         <v>-8.1053</v>
       </c>
       <c r="I455">
-        <v>-0.1222131578947368</v>
+        <v>-0.1222131578947369</v>
       </c>
       <c r="J455">
         <v>6.5</v>
@@ -18547,7 +18547,7 @@
         <v>-6.5511</v>
       </c>
       <c r="I461">
-        <v>0.06782017543859649</v>
+        <v>0.06782017543859652</v>
       </c>
       <c r="J461">
         <v>6.5</v>
@@ -18623,7 +18623,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I463">
-        <v>-0.005909649122807066</v>
+        <v>-0.005909649122807034</v>
       </c>
       <c r="J463">
         <v>6.5</v>
@@ -18661,7 +18661,7 @@
         <v>-4.248</v>
       </c>
       <c r="I464">
-        <v>-0.2478280701754386</v>
+        <v>-0.2478280701754387</v>
       </c>
       <c r="J464">
         <v>6.5</v>
@@ -18737,7 +18737,7 @@
         <v>-7.7634</v>
       </c>
       <c r="I466">
-        <v>-0.07643596491228072</v>
+        <v>-0.07643596491228073</v>
       </c>
       <c r="J466">
         <v>6.5</v>
@@ -18889,7 +18889,7 @@
         <v>-4.958</v>
       </c>
       <c r="I470">
-        <v>0.01515087719298248</v>
+        <v>0.01515087719298246</v>
       </c>
       <c r="J470">
         <v>6.5</v>
@@ -19307,7 +19307,7 @@
         <v>-8.370699999999999</v>
       </c>
       <c r="I481">
-        <v>0.2160754385964913</v>
+        <v>0.2160754385964912</v>
       </c>
       <c r="J481">
         <v>6.5</v>
@@ -19725,7 +19725,7 @@
         <v>-5.1068</v>
       </c>
       <c r="I492">
-        <v>0.09810263157894739</v>
+        <v>0.0981026315789474</v>
       </c>
       <c r="J492">
         <v>6.5</v>
@@ -20523,7 +20523,7 @@
         <v>-7.7903</v>
       </c>
       <c r="I513">
-        <v>0.6595526315789473</v>
+        <v>0.6595526315789474</v>
       </c>
       <c r="J513">
         <v>6.5</v>
@@ -20675,7 +20675,7 @@
         <v>-8.1221</v>
       </c>
       <c r="I517">
-        <v>0.394961403508772</v>
+        <v>0.3949614035087719</v>
       </c>
       <c r="J517">
         <v>6.5</v>
@@ -20865,7 +20865,7 @@
         <v>-5.2765</v>
       </c>
       <c r="I522">
-        <v>-0.04416403508771927</v>
+        <v>-0.04416403508771929</v>
       </c>
       <c r="J522">
         <v>6.5</v>
@@ -21321,7 +21321,7 @@
         <v>-6.5012</v>
       </c>
       <c r="I534">
-        <v>-0.6669587719298246</v>
+        <v>-0.6669587719298247</v>
       </c>
       <c r="J534">
         <v>6.5</v>
@@ -21397,7 +21397,7 @@
         <v>-5.1151</v>
       </c>
       <c r="I536">
-        <v>0.09153333333333334</v>
+        <v>0.09153333333333333</v>
       </c>
       <c r="J536">
         <v>6.5</v>
@@ -22005,7 +22005,7 @@
         <v>-5.5816</v>
       </c>
       <c r="I552">
-        <v>0.09724473684210529</v>
+        <v>0.09724473684210526</v>
       </c>
       <c r="J552">
         <v>6.5</v>
@@ -22347,7 +22347,7 @@
         <v>-6.8291</v>
       </c>
       <c r="I561">
-        <v>0.9898657894736841</v>
+        <v>0.9898657894736842</v>
       </c>
       <c r="J561">
         <v>6.5</v>
@@ -22499,7 +22499,7 @@
         <v>-8.0747</v>
       </c>
       <c r="I565">
-        <v>0.5883105263157894</v>
+        <v>0.5883105263157895</v>
       </c>
       <c r="J565">
         <v>6.5</v>
@@ -22765,7 +22765,7 @@
         <v>-5.7136</v>
       </c>
       <c r="I572">
-        <v>0.4658394736842106</v>
+        <v>0.4658394736842105</v>
       </c>
       <c r="J572">
         <v>6.5</v>
@@ -23487,7 +23487,7 @@
         <v>-6.9653</v>
       </c>
       <c r="I591">
-        <v>-0.02084210526315791</v>
+        <v>-0.02084210526315789</v>
       </c>
       <c r="J591">
         <v>6.5</v>
@@ -24209,7 +24209,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I610">
-        <v>-0.05798157894736841</v>
+        <v>-0.05798157894736842</v>
       </c>
       <c r="J610">
         <v>6.5</v>
@@ -24893,7 +24893,7 @@
         <v>-4.9452</v>
       </c>
       <c r="I628">
-        <v>0.4920342105263158</v>
+        <v>0.4920342105263157</v>
       </c>
       <c r="J628">
         <v>6.5</v>
@@ -25045,7 +25045,7 @@
         <v>-5.5515</v>
       </c>
       <c r="I632">
-        <v>0.3501815789473685</v>
+        <v>0.3501815789473684</v>
       </c>
       <c r="J632">
         <v>6.5</v>
@@ -25083,7 +25083,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I633">
-        <v>0.04088859649122806</v>
+        <v>0.04088859649122808</v>
       </c>
       <c r="J633">
         <v>6.5</v>
@@ -25159,7 +25159,7 @@
         <v>-6.532</v>
       </c>
       <c r="I635">
-        <v>0.01685877192982455</v>
+        <v>0.01685877192982454</v>
       </c>
       <c r="J635">
         <v>6.5</v>
@@ -25311,7 +25311,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I639">
-        <v>0.3845070175438596</v>
+        <v>0.3845070175438597</v>
       </c>
       <c r="J639">
         <v>6.5</v>
@@ -25349,7 +25349,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I640">
-        <v>0.6087508771929826</v>
+        <v>0.6087508771929824</v>
       </c>
       <c r="J640">
         <v>6.5</v>
@@ -25729,7 +25729,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I650">
-        <v>-0.2874561403508771</v>
+        <v>-0.2874561403508772</v>
       </c>
       <c r="J650">
         <v>6.5</v>
@@ -26147,7 +26147,7 @@
         <v>-5.7948</v>
       </c>
       <c r="I661">
-        <v>-0.07977982456140346</v>
+        <v>-0.07977982456140351</v>
       </c>
       <c r="J661">
         <v>6.5</v>
@@ -26413,7 +26413,7 @@
         <v>-5.7349</v>
       </c>
       <c r="I668">
-        <v>1.321807017543859</v>
+        <v>1.32180701754386</v>
       </c>
       <c r="J668">
         <v>6.5</v>
@@ -26565,7 +26565,7 @@
         <v>-8.907500000000001</v>
       </c>
       <c r="I672">
-        <v>0.05063859649122809</v>
+        <v>0.05063859649122808</v>
       </c>
       <c r="J672">
         <v>6.5</v>
@@ -27401,7 +27401,7 @@
         <v>-6.3524</v>
       </c>
       <c r="I694">
-        <v>-0.1134263157894737</v>
+        <v>-0.1134263157894736</v>
       </c>
       <c r="J694">
         <v>6.5</v>
@@ -27743,7 +27743,7 @@
         <v>-8.2332</v>
       </c>
       <c r="I703">
-        <v>-0.2289008771929824</v>
+        <v>-0.2289008771929825</v>
       </c>
       <c r="J703">
         <v>6.5</v>
@@ -27819,7 +27819,7 @@
         <v>-5.8816</v>
       </c>
       <c r="I705">
-        <v>1.095228070175439</v>
+        <v>1.095228070175438</v>
       </c>
       <c r="J705">
         <v>6.5</v>
@@ -27857,7 +27857,7 @@
         <v>-7.5699</v>
       </c>
       <c r="I706">
-        <v>0.1680684210526316</v>
+        <v>0.1680684210526315</v>
       </c>
       <c r="J706">
         <v>6.5</v>
@@ -28047,7 +28047,7 @@
         <v>-6.0046</v>
       </c>
       <c r="I711">
-        <v>1.319487719298245</v>
+        <v>1.319487719298246</v>
       </c>
       <c r="J711">
         <v>6.5</v>
@@ -31581,7 +31581,7 @@
         <v>-7.0178</v>
       </c>
       <c r="I804">
-        <v>0.3055201754385965</v>
+        <v>0.3055201754385964</v>
       </c>
       <c r="J804">
         <v>6.5</v>
@@ -32075,7 +32075,7 @@
         <v>-5.9799</v>
       </c>
       <c r="I817">
-        <v>0.8239289473684211</v>
+        <v>0.823928947368421</v>
       </c>
       <c r="J817">
         <v>6.5</v>
@@ -32113,7 +32113,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I818">
-        <v>-0.05369473684210525</v>
+        <v>-0.05369473684210527</v>
       </c>
       <c r="J818">
         <v>6.5</v>
@@ -32189,7 +32189,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I820">
-        <v>0.09694385964912279</v>
+        <v>0.09694385964912278</v>
       </c>
       <c r="J820">
         <v>6.5</v>
@@ -33177,7 +33177,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I846">
-        <v>-0.08320087719298248</v>
+        <v>-0.0832008771929825</v>
       </c>
       <c r="J846">
         <v>6.5</v>
@@ -33595,7 +33595,7 @@
         <v>-5.1365</v>
       </c>
       <c r="I857">
-        <v>0.3506315789473683</v>
+        <v>0.3506315789473684</v>
       </c>
       <c r="J857">
         <v>6.5</v>
@@ -33899,7 +33899,7 @@
         <v>-7.5395</v>
       </c>
       <c r="I865">
-        <v>-0.6852157894736843</v>
+        <v>-0.6852157894736842</v>
       </c>
       <c r="J865">
         <v>6.5</v>
@@ -34127,7 +34127,7 @@
         <v>-5.7904</v>
       </c>
       <c r="I871">
-        <v>-0.01008245614035087</v>
+        <v>-0.01008245614035089</v>
       </c>
       <c r="J871">
         <v>6.5</v>
@@ -34355,7 +34355,7 @@
         <v>-5.1564</v>
       </c>
       <c r="I877">
-        <v>1.370497368421052</v>
+        <v>1.370497368421053</v>
       </c>
       <c r="J877">
         <v>6.5</v>
@@ -34659,7 +34659,7 @@
         <v>-6.3086</v>
       </c>
       <c r="I885">
-        <v>0.2548052631578948</v>
+        <v>0.2548052631578947</v>
       </c>
       <c r="J885">
         <v>6.5</v>
@@ -34773,7 +34773,7 @@
         <v>-5.5022</v>
       </c>
       <c r="I888">
-        <v>0.4009543859649123</v>
+        <v>0.4009543859649122</v>
       </c>
       <c r="J888">
         <v>6.5</v>
@@ -34963,7 +34963,7 @@
         <v>-6.183</v>
       </c>
       <c r="I893">
-        <v>0.7718307017543861</v>
+        <v>0.771830701754386</v>
       </c>
       <c r="J893">
         <v>6.5</v>
@@ -35495,7 +35495,7 @@
         <v>-5.3294</v>
       </c>
       <c r="I907">
-        <v>1.266428070175438</v>
+        <v>1.266428070175439</v>
       </c>
       <c r="J907">
         <v>6.5</v>
@@ -36255,7 +36255,7 @@
         <v>-6.6449</v>
       </c>
       <c r="I927">
-        <v>0.5105999999999999</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J927">
         <v>6.5</v>
@@ -36483,7 +36483,7 @@
         <v>-6.8076</v>
       </c>
       <c r="I933">
-        <v>0.07269473684210526</v>
+        <v>0.07269473684210523</v>
       </c>
       <c r="J933">
         <v>6.5</v>
@@ -36521,7 +36521,7 @@
         <v>-5.8651</v>
       </c>
       <c r="I934">
-        <v>0.09259035087719295</v>
+        <v>0.09259035087719293</v>
       </c>
       <c r="J934">
         <v>6.5</v>
@@ -36673,7 +36673,7 @@
         <v>-4.314</v>
       </c>
       <c r="I938">
-        <v>-0.03864649122807019</v>
+        <v>-0.03864649122807017</v>
       </c>
       <c r="J938">
         <v>6.5</v>
@@ -36711,7 +36711,7 @@
         <v>-5.2237</v>
       </c>
       <c r="I939">
-        <v>0.8830491228070176</v>
+        <v>0.8830491228070175</v>
       </c>
       <c r="J939">
         <v>6.5</v>
@@ -37015,7 +37015,7 @@
         <v>-5.9791</v>
       </c>
       <c r="I947">
-        <v>0.4313964912280703</v>
+        <v>0.4313964912280702</v>
       </c>
       <c r="J947">
         <v>6.5</v>
@@ -37091,7 +37091,7 @@
         <v>-5.5354</v>
       </c>
       <c r="I949">
-        <v>0.2661078947368421</v>
+        <v>0.266107894736842</v>
       </c>
       <c r="J949">
         <v>6.5</v>
@@ -37129,7 +37129,7 @@
         <v>-6.2272</v>
       </c>
       <c r="I950">
-        <v>0.04605309734513276</v>
+        <v>0.04605309734513275</v>
       </c>
       <c r="J950">
         <v>6.5</v>
@@ -37395,7 +37395,7 @@
         <v>-5.1646</v>
       </c>
       <c r="I957">
-        <v>1.965847368421053</v>
+        <v>1.965847368421052</v>
       </c>
       <c r="J957">
         <v>6.5</v>
@@ -37661,7 +37661,7 @@
         <v>-5.9172</v>
       </c>
       <c r="I964">
-        <v>0.3395885964912281</v>
+        <v>0.339588596491228</v>
       </c>
       <c r="J964">
         <v>6.5</v>
@@ -37737,7 +37737,7 @@
         <v>-8.7384</v>
       </c>
       <c r="I966">
-        <v>0.03935526315789472</v>
+        <v>0.03935526315789473</v>
       </c>
       <c r="J966">
         <v>6.5</v>
@@ -38459,7 +38459,7 @@
         <v>-6.8674</v>
       </c>
       <c r="I985">
-        <v>0.1219596491228071</v>
+        <v>0.121959649122807</v>
       </c>
       <c r="J985">
         <v>6.5</v>
@@ -38649,7 +38649,7 @@
         <v>-5.9258</v>
       </c>
       <c r="I990">
-        <v>0.6400684210526317</v>
+        <v>0.6400684210526315</v>
       </c>
       <c r="J990">
         <v>6.5</v>
@@ -39675,7 +39675,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I1017">
-        <v>0.04960877192982456</v>
+        <v>0.04960877192982454</v>
       </c>
       <c r="J1017">
         <v>6.5</v>
@@ -39865,7 +39865,7 @@
         <v>-7.706</v>
       </c>
       <c r="I1022">
-        <v>-0.01646666666666669</v>
+        <v>-0.01646666666666671</v>
       </c>
       <c r="J1022">
         <v>6.5</v>
@@ -40283,7 +40283,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I1033">
-        <v>0.01259649122807014</v>
+        <v>0.01259649122807016</v>
       </c>
       <c r="J1033">
         <v>6.5</v>
@@ -40663,7 +40663,7 @@
         <v>-6.3647</v>
       </c>
       <c r="I1043">
-        <v>0.4170070175438596</v>
+        <v>0.4170070175438597</v>
       </c>
       <c r="J1043">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -1371,7 +1371,7 @@
         <v>-3.2048</v>
       </c>
       <c r="I9">
-        <v>0.1313833333333333</v>
+        <v>0.1313833333333334</v>
       </c>
       <c r="J9">
         <v>6.5</v>
@@ -1827,7 +1827,7 @@
         <v>-7.6155</v>
       </c>
       <c r="I21">
-        <v>0.01529912280701754</v>
+        <v>0.01529912280701755</v>
       </c>
       <c r="J21">
         <v>6.5</v>
@@ -1865,7 +1865,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I22">
-        <v>0.130678947368421</v>
+        <v>0.1306789473684211</v>
       </c>
       <c r="J22">
         <v>6.5</v>
@@ -2017,7 +2017,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I26">
-        <v>-0.05725964912280702</v>
+        <v>-0.05725964912280703</v>
       </c>
       <c r="J26">
         <v>6.5</v>
@@ -2055,7 +2055,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I27">
-        <v>-0.04229736842105265</v>
+        <v>-0.04229736842105261</v>
       </c>
       <c r="J27">
         <v>6.5</v>
@@ -2397,7 +2397,7 @@
         <v>-4.5954</v>
       </c>
       <c r="I36">
-        <v>-0.1184026315789473</v>
+        <v>-0.1184026315789474</v>
       </c>
       <c r="J36">
         <v>6.5</v>
@@ -2891,7 +2891,7 @@
         <v>-4.688</v>
       </c>
       <c r="I49">
-        <v>0.6045543859649123</v>
+        <v>0.6045543859649122</v>
       </c>
       <c r="J49">
         <v>6.5</v>
@@ -2929,7 +2929,7 @@
         <v>-5.1686</v>
       </c>
       <c r="I50">
-        <v>0.06831403508771929</v>
+        <v>0.0683140350877193</v>
       </c>
       <c r="J50">
         <v>6.5</v>
@@ -3081,7 +3081,7 @@
         <v>-7.5421</v>
       </c>
       <c r="I54">
-        <v>-8.771929824579916E-06</v>
+        <v>-8.771929824540839E-06</v>
       </c>
       <c r="J54">
         <v>6.5</v>
@@ -3461,7 +3461,7 @@
         <v>-4.7353</v>
       </c>
       <c r="I64">
-        <v>0.7190307017543861</v>
+        <v>0.7190307017543859</v>
       </c>
       <c r="J64">
         <v>6.5</v>
@@ -3575,7 +3575,7 @@
         <v>-5.1919</v>
       </c>
       <c r="I67">
-        <v>0.3820850877192983</v>
+        <v>0.3820850877192982</v>
       </c>
       <c r="J67">
         <v>6.5</v>
@@ -3651,7 +3651,7 @@
         <v>-5.3978</v>
       </c>
       <c r="I69">
-        <v>0.7009289473684209</v>
+        <v>0.700928947368421</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -4183,7 +4183,7 @@
         <v>-6.1583</v>
       </c>
       <c r="I83">
-        <v>-0.5077052631578947</v>
+        <v>-0.5077052631578948</v>
       </c>
       <c r="J83">
         <v>6.5</v>
@@ -4259,7 +4259,7 @@
         <v>-5.5616</v>
       </c>
       <c r="I85">
-        <v>-0.005708771929824527</v>
+        <v>-0.005708771929824541</v>
       </c>
       <c r="J85">
         <v>6.5</v>
@@ -4373,7 +4373,7 @@
         <v>-4.5504</v>
       </c>
       <c r="I88">
-        <v>0.86665</v>
+        <v>0.8666499999999999</v>
       </c>
       <c r="J88">
         <v>6.5</v>
@@ -4411,7 +4411,7 @@
         <v>-5.5323</v>
       </c>
       <c r="I89">
-        <v>-0.6382342105263158</v>
+        <v>-0.6382342105263157</v>
       </c>
       <c r="J89">
         <v>6.5</v>
@@ -4525,7 +4525,7 @@
         <v>-5.325</v>
       </c>
       <c r="I92">
-        <v>0.06181315789473686</v>
+        <v>0.06181315789473685</v>
       </c>
       <c r="J92">
         <v>6.5</v>
@@ -4563,7 +4563,7 @@
         <v>-5.5639</v>
       </c>
       <c r="I93">
-        <v>0.03160175438596494</v>
+        <v>0.03160175438596489</v>
       </c>
       <c r="J93">
         <v>6.5</v>
@@ -4601,7 +4601,7 @@
         <v>-4.9943</v>
       </c>
       <c r="I94">
-        <v>0.01033684210526312</v>
+        <v>0.01033684210526315</v>
       </c>
       <c r="J94">
         <v>6.5</v>
@@ -5019,7 +5019,7 @@
         <v>-5.7006</v>
       </c>
       <c r="I105">
-        <v>-0.2644166666666666</v>
+        <v>-0.2644166666666667</v>
       </c>
       <c r="J105">
         <v>6.5</v>
@@ -5133,7 +5133,7 @@
         <v>-4.9181</v>
       </c>
       <c r="I108">
-        <v>0.6396736842105263</v>
+        <v>0.6396736842105264</v>
       </c>
       <c r="J108">
         <v>6.5</v>
@@ -5209,7 +5209,7 @@
         <v>-7.6593</v>
       </c>
       <c r="I110">
-        <v>-0.304978947368421</v>
+        <v>-0.3049789473684211</v>
       </c>
       <c r="J110">
         <v>6.5</v>
@@ -5475,7 +5475,7 @@
         <v>-4.7549</v>
       </c>
       <c r="I117">
-        <v>-0.09559736842105261</v>
+        <v>-0.09559736842105258</v>
       </c>
       <c r="J117">
         <v>6.5</v>
@@ -5551,7 +5551,7 @@
         <v>-4.9268</v>
       </c>
       <c r="I119">
-        <v>0.1207350877192982</v>
+        <v>0.1207350877192983</v>
       </c>
       <c r="J119">
         <v>6.5</v>
@@ -5665,7 +5665,7 @@
         <v>-4.8973</v>
       </c>
       <c r="I122">
-        <v>0.3157789473684211</v>
+        <v>0.315778947368421</v>
       </c>
       <c r="J122">
         <v>6.5</v>
@@ -5703,7 +5703,7 @@
         <v>-6.387</v>
       </c>
       <c r="I123">
-        <v>-0.1918429824561403</v>
+        <v>-0.1918429824561404</v>
       </c>
       <c r="J123">
         <v>6.5</v>
@@ -5817,7 +5817,7 @@
         <v>-4.8548</v>
       </c>
       <c r="I126">
-        <v>-0.020229203539823</v>
+        <v>-0.02022920353982298</v>
       </c>
       <c r="J126">
         <v>6.5</v>
@@ -6045,7 +6045,7 @@
         <v>-4.7021</v>
       </c>
       <c r="I132">
-        <v>-0.04365350877192985</v>
+        <v>-0.04365350877192984</v>
       </c>
       <c r="J132">
         <v>6.5</v>
@@ -6083,7 +6083,7 @@
         <v>-4.7964</v>
       </c>
       <c r="I133">
-        <v>0.8078719298245614</v>
+        <v>0.8078719298245615</v>
       </c>
       <c r="J133">
         <v>6.5</v>
@@ -6235,7 +6235,7 @@
         <v>-6.3804</v>
       </c>
       <c r="I137">
-        <v>0.01184473684210525</v>
+        <v>0.01184473684210523</v>
       </c>
       <c r="J137">
         <v>6.5</v>
@@ -6273,7 +6273,7 @@
         <v>-6.1406</v>
       </c>
       <c r="I138">
-        <v>-0.1075850877192983</v>
+        <v>-0.1075850877192982</v>
       </c>
       <c r="J138">
         <v>6.5</v>
@@ -6349,7 +6349,7 @@
         <v>-5.4954</v>
       </c>
       <c r="I140">
-        <v>-0.07092123893805302</v>
+        <v>-0.07092123893805306</v>
       </c>
       <c r="J140">
         <v>6.5</v>
@@ -6501,7 +6501,7 @@
         <v>-4.9361</v>
       </c>
       <c r="I144">
-        <v>0.4951833333333334</v>
+        <v>0.4951833333333333</v>
       </c>
       <c r="J144">
         <v>6.5</v>
@@ -6767,7 +6767,7 @@
         <v>-5.5488</v>
       </c>
       <c r="I151">
-        <v>-0.09169736842105264</v>
+        <v>-0.09169736842105261</v>
       </c>
       <c r="J151">
         <v>6.5</v>
@@ -7071,7 +7071,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I159">
-        <v>0.0347070175438596</v>
+        <v>0.03470701754385963</v>
       </c>
       <c r="J159">
         <v>6.5</v>
@@ -7109,7 +7109,7 @@
         <v>-5.1599</v>
       </c>
       <c r="I160">
-        <v>-0.4605105263157894</v>
+        <v>-0.4605105263157895</v>
       </c>
       <c r="J160">
         <v>6.5</v>
@@ -7185,7 +7185,7 @@
         <v>-5.8107</v>
       </c>
       <c r="I162">
-        <v>-0.5701219298245614</v>
+        <v>-0.5701219298245613</v>
       </c>
       <c r="J162">
         <v>6.5</v>
@@ -7337,7 +7337,7 @@
         <v>-5.0848</v>
       </c>
       <c r="I166">
-        <v>-0.5323552631578948</v>
+        <v>-0.5323552631578947</v>
       </c>
       <c r="J166">
         <v>6.5</v>
@@ -7527,7 +7527,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I171">
-        <v>-0.04652807017543856</v>
+        <v>-0.04652807017543858</v>
       </c>
       <c r="J171">
         <v>6.5</v>
@@ -7983,7 +7983,7 @@
         <v>-6.4771</v>
       </c>
       <c r="I183">
-        <v>-0.3391140350877194</v>
+        <v>-0.3391140350877193</v>
       </c>
       <c r="J183">
         <v>6.5</v>
@@ -8021,7 +8021,7 @@
         <v>-8.4955</v>
       </c>
       <c r="I184">
-        <v>0.5397631578947369</v>
+        <v>0.5397631578947368</v>
       </c>
       <c r="J184">
         <v>6.5</v>
@@ -8059,7 +8059,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I185">
-        <v>-0.008549999999999995</v>
+        <v>-0.008549999999999988</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -8173,7 +8173,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I188">
-        <v>-0.0523719298245614</v>
+        <v>-0.05237192982456138</v>
       </c>
       <c r="J188">
         <v>6.5</v>
@@ -8325,7 +8325,7 @@
         <v>-4.7361</v>
       </c>
       <c r="I192">
-        <v>0.3821929824561403</v>
+        <v>0.3821929824561404</v>
       </c>
       <c r="J192">
         <v>6.5</v>
@@ -8363,7 +8363,7 @@
         <v>-6.5935</v>
       </c>
       <c r="I193">
-        <v>-0.2784456140350878</v>
+        <v>-0.2784456140350877</v>
       </c>
       <c r="J193">
         <v>6.5</v>
@@ -8477,7 +8477,7 @@
         <v>-4.9463</v>
       </c>
       <c r="I196">
-        <v>0.1976649122807017</v>
+        <v>0.1976649122807018</v>
       </c>
       <c r="J196">
         <v>6.5</v>
@@ -8705,7 +8705,7 @@
         <v>-5.0406</v>
       </c>
       <c r="I202">
-        <v>-0.07873333333333334</v>
+        <v>-0.07873333333333335</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8743,7 +8743,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I203">
-        <v>1.477787719298245</v>
+        <v>1.477787719298246</v>
       </c>
       <c r="J203">
         <v>6.5</v>
@@ -8857,7 +8857,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I206">
-        <v>-0.00677456140350876</v>
+        <v>-0.006774561403508784</v>
       </c>
       <c r="J206">
         <v>6.5</v>
@@ -8971,7 +8971,7 @@
         <v>-4.2809</v>
       </c>
       <c r="I209">
-        <v>0.7727947368421052</v>
+        <v>0.7727947368421053</v>
       </c>
       <c r="J209">
         <v>6.5</v>
@@ -9161,7 +9161,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I214">
-        <v>0.09611228070175441</v>
+        <v>0.0961122807017544</v>
       </c>
       <c r="J214">
         <v>6.5</v>
@@ -9199,7 +9199,7 @@
         <v>-7.404</v>
       </c>
       <c r="I215">
-        <v>0.5225359649122806</v>
+        <v>0.5225359649122807</v>
       </c>
       <c r="J215">
         <v>6.5</v>
@@ -9275,7 +9275,7 @@
         <v>-6.421</v>
       </c>
       <c r="I217">
-        <v>0.7688903508771929</v>
+        <v>0.768890350877193</v>
       </c>
       <c r="J217">
         <v>6.5</v>
@@ -10111,7 +10111,7 @@
         <v>-6.8644</v>
       </c>
       <c r="I239">
-        <v>-0.3149601769911504</v>
+        <v>-0.3149601769911505</v>
       </c>
       <c r="J239">
         <v>6.5</v>
@@ -10301,7 +10301,7 @@
         <v>-7.8256</v>
       </c>
       <c r="I244">
-        <v>0.03879035087719299</v>
+        <v>0.038790350877193</v>
       </c>
       <c r="J244">
         <v>6.5</v>
@@ -10643,7 +10643,7 @@
         <v>-8.3277</v>
       </c>
       <c r="I253">
-        <v>-0.9198491228070175</v>
+        <v>-0.9198491228070176</v>
       </c>
       <c r="J253">
         <v>6.5</v>
@@ -10833,7 +10833,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I258">
-        <v>0.03353596491228067</v>
+        <v>0.0335359649122807</v>
       </c>
       <c r="J258">
         <v>6.5</v>
@@ -11213,7 +11213,7 @@
         <v>-7.0616</v>
       </c>
       <c r="I268">
-        <v>0.3301157894736843</v>
+        <v>0.3301157894736841</v>
       </c>
       <c r="J268">
         <v>6.5</v>
@@ -11365,7 +11365,7 @@
         <v>-6.9621</v>
       </c>
       <c r="I272">
-        <v>-0.2529184210526316</v>
+        <v>-0.2529184210526315</v>
       </c>
       <c r="J272">
         <v>6.5</v>
@@ -11631,7 +11631,7 @@
         <v>-8.186500000000001</v>
       </c>
       <c r="I279">
-        <v>0.7274377192982456</v>
+        <v>0.7274377192982455</v>
       </c>
       <c r="J279">
         <v>6.5</v>
@@ -11821,7 +11821,7 @@
         <v>-5.579</v>
       </c>
       <c r="I284">
-        <v>0.03944473684210525</v>
+        <v>0.03944473684210526</v>
       </c>
       <c r="J284">
         <v>6.5</v>
@@ -11897,7 +11897,7 @@
         <v>-4.7368</v>
       </c>
       <c r="I286">
-        <v>1.702028070175438</v>
+        <v>1.702028070175439</v>
       </c>
       <c r="J286">
         <v>6.5</v>
@@ -12049,7 +12049,7 @@
         <v>-3.9858</v>
       </c>
       <c r="I290">
-        <v>2.774078070175438</v>
+        <v>2.774078070175439</v>
       </c>
       <c r="J290">
         <v>6.5</v>
@@ -12353,7 +12353,7 @@
         <v>-5.9669</v>
       </c>
       <c r="I298">
-        <v>-0.177709649122807</v>
+        <v>-0.1777096491228071</v>
       </c>
       <c r="J298">
         <v>6.5</v>
@@ -12467,7 +12467,7 @@
         <v>-7.4805</v>
       </c>
       <c r="I301">
-        <v>0.08061228070175434</v>
+        <v>0.08061228070175436</v>
       </c>
       <c r="J301">
         <v>6.5</v>
@@ -12695,7 +12695,7 @@
         <v>-8.475300000000001</v>
       </c>
       <c r="I307">
-        <v>0.6196201754385964</v>
+        <v>0.6196201754385965</v>
       </c>
       <c r="J307">
         <v>6.5</v>
@@ -13341,7 +13341,7 @@
         <v>-5.1407</v>
       </c>
       <c r="I324">
-        <v>0.2866377192982456</v>
+        <v>0.2866377192982457</v>
       </c>
       <c r="J324">
         <v>6.5</v>
@@ -13455,7 +13455,7 @@
         <v>-8.5182</v>
       </c>
       <c r="I327">
-        <v>0.8065350877192982</v>
+        <v>0.8065350877192983</v>
       </c>
       <c r="J327">
         <v>6.5</v>
@@ -13531,7 +13531,7 @@
         <v>-10.5468</v>
       </c>
       <c r="I329">
-        <v>-0.06476842105263157</v>
+        <v>-0.06476842105263154</v>
       </c>
       <c r="J329">
         <v>6.5</v>
@@ -13645,7 +13645,7 @@
         <v>-4.5464</v>
       </c>
       <c r="I332">
-        <v>0.7982622807017543</v>
+        <v>0.7982622807017544</v>
       </c>
       <c r="J332">
         <v>6.5</v>
@@ -13721,7 +13721,7 @@
         <v>-4.7487</v>
       </c>
       <c r="I334">
-        <v>-0.01714210526315788</v>
+        <v>-0.01714210526315789</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -13797,7 +13797,7 @@
         <v>-4.3643</v>
       </c>
       <c r="I336">
-        <v>0.6671412280701755</v>
+        <v>0.6671412280701754</v>
       </c>
       <c r="J336">
         <v>6.5</v>
@@ -14785,7 +14785,7 @@
         <v>-5.1904</v>
       </c>
       <c r="I362">
-        <v>0.05131228070175436</v>
+        <v>0.05131228070175438</v>
       </c>
       <c r="J362">
         <v>6.5</v>
@@ -14861,7 +14861,7 @@
         <v>-9.506500000000001</v>
       </c>
       <c r="I364">
-        <v>0.9554911504424779</v>
+        <v>0.9554911504424778</v>
       </c>
       <c r="J364">
         <v>6.5</v>
@@ -15051,7 +15051,7 @@
         <v>-7.5056</v>
       </c>
       <c r="I369">
-        <v>0.8824122807017544</v>
+        <v>0.8824122807017545</v>
       </c>
       <c r="J369">
         <v>6.5</v>
@@ -15393,7 +15393,7 @@
         <v>-5.1258</v>
       </c>
       <c r="I378">
-        <v>0.7531894736842105</v>
+        <v>0.7531894736842104</v>
       </c>
       <c r="J378">
         <v>6.5</v>
@@ -15659,7 +15659,7 @@
         <v>-4.642</v>
       </c>
       <c r="I385">
-        <v>0.1400105263157894</v>
+        <v>0.1400105263157895</v>
       </c>
       <c r="J385">
         <v>6.5</v>
@@ -15849,7 +15849,7 @@
         <v>-4.5944</v>
       </c>
       <c r="I390">
-        <v>0.7309088495575222</v>
+        <v>0.7309088495575221</v>
       </c>
       <c r="J390">
         <v>6.5</v>
@@ -16039,7 +16039,7 @@
         <v>-6.718</v>
       </c>
       <c r="I395">
-        <v>0.5547491228070175</v>
+        <v>0.5547491228070176</v>
       </c>
       <c r="J395">
         <v>6.5</v>
@@ -16153,7 +16153,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I398">
-        <v>0.8492342105263159</v>
+        <v>0.8492342105263158</v>
       </c>
       <c r="J398">
         <v>6.5</v>
@@ -16343,7 +16343,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I403">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J403">
         <v>6.5</v>
@@ -17445,7 +17445,7 @@
         <v>-7.3019</v>
       </c>
       <c r="I432">
-        <v>0.1687754385964913</v>
+        <v>0.1687754385964912</v>
       </c>
       <c r="J432">
         <v>6.5</v>
@@ -18547,7 +18547,7 @@
         <v>-6.5511</v>
       </c>
       <c r="I461">
-        <v>0.06782017543859648</v>
+        <v>0.06782017543859652</v>
       </c>
       <c r="J461">
         <v>6.5</v>
@@ -18623,7 +18623,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I463">
-        <v>-0.00590964912280705</v>
+        <v>-0.005909649122807058</v>
       </c>
       <c r="J463">
         <v>6.5</v>
@@ -18661,7 +18661,7 @@
         <v>-4.248</v>
       </c>
       <c r="I464">
-        <v>-0.2478280701754386</v>
+        <v>-0.2478280701754387</v>
       </c>
       <c r="J464">
         <v>6.5</v>
@@ -18699,7 +18699,7 @@
         <v>-4.8506</v>
       </c>
       <c r="I465">
-        <v>-0.8625052631578948</v>
+        <v>-0.8625052631578947</v>
       </c>
       <c r="J465">
         <v>6.5</v>
@@ -18737,7 +18737,7 @@
         <v>-7.7634</v>
       </c>
       <c r="I466">
-        <v>-0.07643596491228072</v>
+        <v>-0.07643596491228073</v>
       </c>
       <c r="J466">
         <v>6.5</v>
@@ -18889,7 +18889,7 @@
         <v>-4.958</v>
       </c>
       <c r="I470">
-        <v>0.01515087719298248</v>
+        <v>0.01515087719298245</v>
       </c>
       <c r="J470">
         <v>6.5</v>
@@ -19193,7 +19193,7 @@
         <v>-5.6928</v>
       </c>
       <c r="I478">
-        <v>0.7451429824561404</v>
+        <v>0.7451429824561403</v>
       </c>
       <c r="J478">
         <v>6.5</v>
@@ -19345,7 +19345,7 @@
         <v>-4.9353</v>
       </c>
       <c r="I482">
-        <v>0.481109649122807</v>
+        <v>0.4811096491228071</v>
       </c>
       <c r="J482">
         <v>6.5</v>
@@ -19497,7 +19497,7 @@
         <v>-5.0702</v>
       </c>
       <c r="I486">
-        <v>0.412380701754386</v>
+        <v>0.4123807017543859</v>
       </c>
       <c r="J486">
         <v>6.5</v>
@@ -19535,7 +19535,7 @@
         <v>-7.0157</v>
       </c>
       <c r="I487">
-        <v>0.9124140350877193</v>
+        <v>0.9124140350877192</v>
       </c>
       <c r="J487">
         <v>6.5</v>
@@ -19725,7 +19725,7 @@
         <v>-5.1068</v>
       </c>
       <c r="I492">
-        <v>0.09810263157894736</v>
+        <v>0.09810263157894739</v>
       </c>
       <c r="J492">
         <v>6.5</v>
@@ -19801,7 +19801,7 @@
         <v>-6.0853</v>
       </c>
       <c r="I494">
-        <v>-0.4788771929824562</v>
+        <v>-0.4788771929824561</v>
       </c>
       <c r="J494">
         <v>6.5</v>
@@ -19877,7 +19877,7 @@
         <v>-4.3611</v>
       </c>
       <c r="I496">
-        <v>0.5711991228070175</v>
+        <v>0.5711991228070176</v>
       </c>
       <c r="J496">
         <v>6.5</v>
@@ -20257,7 +20257,7 @@
         <v>-6.9126</v>
       </c>
       <c r="I506">
-        <v>-0.00701754385964911</v>
+        <v>-0.007017543859649121</v>
       </c>
       <c r="J506">
         <v>6.5</v>
@@ -20295,7 +20295,7 @@
         <v>-6.6796</v>
       </c>
       <c r="I507">
-        <v>1.50831052631579</v>
+        <v>1.508310526315789</v>
       </c>
       <c r="J507">
         <v>6.5</v>
@@ -20675,7 +20675,7 @@
         <v>-8.1221</v>
       </c>
       <c r="I517">
-        <v>0.394961403508772</v>
+        <v>0.3949614035087719</v>
       </c>
       <c r="J517">
         <v>6.5</v>
@@ -20865,7 +20865,7 @@
         <v>-5.2765</v>
       </c>
       <c r="I522">
-        <v>-0.04416403508771929</v>
+        <v>-0.04416403508771931</v>
       </c>
       <c r="J522">
         <v>6.5</v>
@@ -21397,7 +21397,7 @@
         <v>-5.1151</v>
       </c>
       <c r="I536">
-        <v>0.09153333333333333</v>
+        <v>0.0915333333333333</v>
       </c>
       <c r="J536">
         <v>6.5</v>
@@ -21587,7 +21587,7 @@
         <v>-7.8784</v>
       </c>
       <c r="I541">
-        <v>-0.1674350877192982</v>
+        <v>-0.1674350877192983</v>
       </c>
       <c r="J541">
         <v>6.5</v>
@@ -21701,7 +21701,7 @@
         <v>-7.3353</v>
       </c>
       <c r="I544">
-        <v>-0.631270796460177</v>
+        <v>-0.6312707964601769</v>
       </c>
       <c r="J544">
         <v>6.5</v>
@@ -22005,7 +22005,7 @@
         <v>-5.5816</v>
       </c>
       <c r="I552">
-        <v>0.09724473684210526</v>
+        <v>0.09724473684210529</v>
       </c>
       <c r="J552">
         <v>6.5</v>
@@ -22347,7 +22347,7 @@
         <v>-6.8291</v>
       </c>
       <c r="I561">
-        <v>0.9898657894736842</v>
+        <v>0.9898657894736841</v>
       </c>
       <c r="J561">
         <v>6.5</v>
@@ -22499,7 +22499,7 @@
         <v>-8.0747</v>
       </c>
       <c r="I565">
-        <v>0.5883105263157894</v>
+        <v>0.5883105263157895</v>
       </c>
       <c r="J565">
         <v>6.5</v>
@@ -22765,7 +22765,7 @@
         <v>-5.7136</v>
       </c>
       <c r="I572">
-        <v>0.4658394736842105</v>
+        <v>0.4658394736842106</v>
       </c>
       <c r="J572">
         <v>6.5</v>
@@ -23487,7 +23487,7 @@
         <v>-6.9653</v>
       </c>
       <c r="I591">
-        <v>-0.02084210526315787</v>
+        <v>-0.02084210526315789</v>
       </c>
       <c r="J591">
         <v>6.5</v>
@@ -23791,7 +23791,7 @@
         <v>-6.5046</v>
       </c>
       <c r="I599">
-        <v>0.7791377192982457</v>
+        <v>0.7791377192982456</v>
       </c>
       <c r="J599">
         <v>6.5</v>
@@ -24057,7 +24057,7 @@
         <v>-4.9538</v>
       </c>
       <c r="I606">
-        <v>0.614871052631579</v>
+        <v>0.6148710526315789</v>
       </c>
       <c r="J606">
         <v>6.5</v>
@@ -24209,7 +24209,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I610">
-        <v>-0.05798157894736838</v>
+        <v>-0.0579815789473684</v>
       </c>
       <c r="J610">
         <v>6.5</v>
@@ -24779,7 +24779,7 @@
         <v>-5.8156</v>
       </c>
       <c r="I625">
-        <v>0.3542000000000001</v>
+        <v>0.3542</v>
       </c>
       <c r="J625">
         <v>6.5</v>
@@ -25083,7 +25083,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I633">
-        <v>0.04088859649122807</v>
+        <v>0.04088859649122804</v>
       </c>
       <c r="J633">
         <v>6.5</v>
@@ -25311,7 +25311,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I639">
-        <v>0.3845070175438597</v>
+        <v>0.3845070175438596</v>
       </c>
       <c r="J639">
         <v>6.5</v>
@@ -25349,7 +25349,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I640">
-        <v>0.6087508771929826</v>
+        <v>0.6087508771929824</v>
       </c>
       <c r="J640">
         <v>6.5</v>
@@ -25615,7 +25615,7 @@
         <v>-7.8297</v>
       </c>
       <c r="I647">
-        <v>0.3773359649122808</v>
+        <v>0.3773359649122807</v>
       </c>
       <c r="J647">
         <v>6.5</v>
@@ -25729,7 +25729,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I650">
-        <v>-0.2874561403508772</v>
+        <v>-0.2874561403508771</v>
       </c>
       <c r="J650">
         <v>6.5</v>
@@ -25805,7 +25805,7 @@
         <v>-3.3104</v>
       </c>
       <c r="I652">
-        <v>0.8435719298245615</v>
+        <v>0.8435719298245613</v>
       </c>
       <c r="J652">
         <v>6.5</v>
@@ -26033,7 +26033,7 @@
         <v>-6.2062</v>
       </c>
       <c r="I658">
-        <v>0.3236368421052632</v>
+        <v>0.3236368421052631</v>
       </c>
       <c r="J658">
         <v>6.5</v>
@@ -26147,7 +26147,7 @@
         <v>-5.7948</v>
       </c>
       <c r="I661">
-        <v>-0.07977982456140348</v>
+        <v>-0.07977982456140346</v>
       </c>
       <c r="J661">
         <v>6.5</v>
@@ -26565,7 +26565,7 @@
         <v>-8.907500000000001</v>
       </c>
       <c r="I672">
-        <v>0.05063859649122814</v>
+        <v>0.05063859649122807</v>
       </c>
       <c r="J672">
         <v>6.5</v>
@@ -26831,7 +26831,7 @@
         <v>-6.7926</v>
       </c>
       <c r="I679">
-        <v>0.7803175438596492</v>
+        <v>0.7803175438596491</v>
       </c>
       <c r="J679">
         <v>6.5</v>
@@ -27401,7 +27401,7 @@
         <v>-6.3524</v>
       </c>
       <c r="I694">
-        <v>-0.1134263157894736</v>
+        <v>-0.1134263157894737</v>
       </c>
       <c r="J694">
         <v>6.5</v>
@@ -28199,7 +28199,7 @@
         <v>-5.1964</v>
       </c>
       <c r="I715">
-        <v>0.2435859649122807</v>
+        <v>0.2435859649122808</v>
       </c>
       <c r="J715">
         <v>6.5</v>
@@ -28807,7 +28807,7 @@
         <v>-4.6952</v>
       </c>
       <c r="I731">
-        <v>-0.2975912280701754</v>
+        <v>-0.2975912280701755</v>
       </c>
       <c r="J731">
         <v>6.5</v>
@@ -28883,7 +28883,7 @@
         <v>-5.3226</v>
       </c>
       <c r="I733">
-        <v>-0.3628570175438596</v>
+        <v>-0.3628570175438597</v>
       </c>
       <c r="J733">
         <v>6.5</v>
@@ -28997,7 +28997,7 @@
         <v>-5.3058</v>
       </c>
       <c r="I736">
-        <v>1.014541228070176</v>
+        <v>1.014541228070175</v>
       </c>
       <c r="J736">
         <v>6.5</v>
@@ -29491,7 +29491,7 @@
         <v>-6.2194</v>
       </c>
       <c r="I749">
-        <v>0.4190657894736843</v>
+        <v>0.4190657894736842</v>
       </c>
       <c r="J749">
         <v>6.5</v>
@@ -29757,7 +29757,7 @@
         <v>-7.4388</v>
       </c>
       <c r="I756">
-        <v>0.8952345132743363</v>
+        <v>0.8952345132743362</v>
       </c>
       <c r="J756">
         <v>6.5</v>
@@ -31125,7 +31125,7 @@
         <v>-6.9108</v>
       </c>
       <c r="I792">
-        <v>0.7567771929824562</v>
+        <v>0.7567771929824563</v>
       </c>
       <c r="J792">
         <v>6.5</v>
@@ -31201,7 +31201,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I794">
-        <v>0.4163964912280702</v>
+        <v>0.4163964912280703</v>
       </c>
       <c r="J794">
         <v>6.5</v>
@@ -32189,7 +32189,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I820">
-        <v>0.09694385964912278</v>
+        <v>0.09694385964912279</v>
       </c>
       <c r="J820">
         <v>6.5</v>
@@ -33177,7 +33177,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I846">
-        <v>-0.08320087719298246</v>
+        <v>-0.08320087719298248</v>
       </c>
       <c r="J846">
         <v>6.5</v>
@@ -33253,7 +33253,7 @@
         <v>-4.6814</v>
       </c>
       <c r="I848">
-        <v>1.404900877192983</v>
+        <v>1.404900877192982</v>
       </c>
       <c r="J848">
         <v>6.5</v>
@@ -33405,7 +33405,7 @@
         <v>-5.9691</v>
       </c>
       <c r="I852">
-        <v>-0.09673684210526313</v>
+        <v>-0.09673684210526315</v>
       </c>
       <c r="J852">
         <v>6.5</v>
@@ -33481,7 +33481,7 @@
         <v>-6.8676</v>
       </c>
       <c r="I854">
-        <v>-0.05854690265486726</v>
+        <v>-0.05854690265486728</v>
       </c>
       <c r="J854">
         <v>6.5</v>
@@ -33595,7 +33595,7 @@
         <v>-5.1365</v>
       </c>
       <c r="I857">
-        <v>0.3506315789473683</v>
+        <v>0.3506315789473684</v>
       </c>
       <c r="J857">
         <v>6.5</v>
@@ -33747,7 +33747,7 @@
         <v>-5.1786</v>
       </c>
       <c r="I861">
-        <v>0.1879947368421053</v>
+        <v>0.1879947368421052</v>
       </c>
       <c r="J861">
         <v>6.5</v>
@@ -34127,7 +34127,7 @@
         <v>-5.7904</v>
       </c>
       <c r="I871">
-        <v>-0.01008245614035089</v>
+        <v>-0.01008245614035088</v>
       </c>
       <c r="J871">
         <v>6.5</v>
@@ -34317,7 +34317,7 @@
         <v>-5.6437</v>
       </c>
       <c r="I876">
-        <v>0.9088657894736842</v>
+        <v>0.9088657894736841</v>
       </c>
       <c r="J876">
         <v>6.5</v>
@@ -34355,7 +34355,7 @@
         <v>-5.1564</v>
       </c>
       <c r="I877">
-        <v>1.370497368421052</v>
+        <v>1.370497368421053</v>
       </c>
       <c r="J877">
         <v>6.5</v>
@@ -35077,7 +35077,7 @@
         <v>-5.324</v>
       </c>
       <c r="I896">
-        <v>0.9111149122807017</v>
+        <v>0.9111149122807018</v>
       </c>
       <c r="J896">
         <v>6.5</v>
@@ -35495,7 +35495,7 @@
         <v>-5.3294</v>
       </c>
       <c r="I907">
-        <v>1.266428070175439</v>
+        <v>1.266428070175438</v>
       </c>
       <c r="J907">
         <v>6.5</v>
@@ -35647,7 +35647,7 @@
         <v>-5.3179</v>
       </c>
       <c r="I911">
-        <v>0.9225447368421054</v>
+        <v>0.9225447368421051</v>
       </c>
       <c r="J911">
         <v>6.5</v>
@@ -36521,7 +36521,7 @@
         <v>-5.8651</v>
       </c>
       <c r="I934">
-        <v>0.09259035087719297</v>
+        <v>0.09259035087719295</v>
       </c>
       <c r="J934">
         <v>6.5</v>
@@ -36673,7 +36673,7 @@
         <v>-4.314</v>
       </c>
       <c r="I938">
-        <v>-0.0386464912280702</v>
+        <v>-0.03864649122807019</v>
       </c>
       <c r="J938">
         <v>6.5</v>
@@ -38307,7 +38307,7 @@
         <v>-4.9665</v>
       </c>
       <c r="I981">
-        <v>0.3751578947368422</v>
+        <v>0.3751578947368421</v>
       </c>
       <c r="J981">
         <v>6.5</v>
@@ -39675,7 +39675,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I1017">
-        <v>0.04960877192982453</v>
+        <v>0.04960877192982457</v>
       </c>
       <c r="J1017">
         <v>6.5</v>
@@ -39865,7 +39865,7 @@
         <v>-7.706</v>
       </c>
       <c r="I1022">
-        <v>-0.01646666666666672</v>
+        <v>-0.0164666666666667</v>
       </c>
       <c r="J1022">
         <v>6.5</v>
@@ -40207,7 +40207,7 @@
         <v>-7.3081</v>
       </c>
       <c r="I1031">
-        <v>0.06260964912280703</v>
+        <v>0.06260964912280705</v>
       </c>
       <c r="J1031">
         <v>6.5</v>
@@ -40283,7 +40283,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I1033">
-        <v>0.01259649122807016</v>
+        <v>0.01259649122807015</v>
       </c>
       <c r="J1033">
         <v>6.5</v>
@@ -40321,7 +40321,7 @@
         <v>-6.279</v>
       </c>
       <c r="I1034">
-        <v>0.9070438596491228</v>
+        <v>0.9070438596491227</v>
       </c>
       <c r="J1034">
         <v>6.5</v>
@@ -40511,7 +40511,7 @@
         <v>-4.8149</v>
       </c>
       <c r="I1039">
-        <v>0.5483412280701754</v>
+        <v>0.5483412280701755</v>
       </c>
       <c r="J1039">
         <v>6.5</v>
@@ -40663,7 +40663,7 @@
         <v>-6.3647</v>
       </c>
       <c r="I1043">
-        <v>0.4170070175438596</v>
+        <v>0.4170070175438597</v>
       </c>
       <c r="J1043">
         <v>6.5</v>
@@ -40739,7 +40739,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I1045">
-        <v>0.5621114035087719</v>
+        <v>0.562111403508772</v>
       </c>
       <c r="J1045">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -715,7 +715,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I2">
-        <v>0.130678947368421</v>
+        <v>0.1306789473684211</v>
       </c>
       <c r="J2">
         <v>6.5</v>
@@ -867,7 +867,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I6">
-        <v>-0.05725964912280702</v>
+        <v>-0.057259649122807</v>
       </c>
       <c r="J6">
         <v>6.5</v>
@@ -905,7 +905,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I7">
-        <v>-0.04229736842105265</v>
+        <v>-0.04229736842105261</v>
       </c>
       <c r="J7">
         <v>6.5</v>
@@ -2083,7 +2083,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I38">
-        <v>-0.008550000000000051</v>
+        <v>-0.008549999999999988</v>
       </c>
       <c r="J38">
         <v>6.5</v>
@@ -2197,7 +2197,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I41">
-        <v>-0.05237192982456138</v>
+        <v>-0.0523719298245614</v>
       </c>
       <c r="J41">
         <v>6.5</v>
@@ -2235,7 +2235,7 @@
         <v>-5.7267</v>
       </c>
       <c r="I42">
-        <v>0.3732684210526316</v>
+        <v>0.3732684210526315</v>
       </c>
       <c r="J42">
         <v>6.5</v>
@@ -2387,7 +2387,7 @@
         <v>-6.5935</v>
       </c>
       <c r="I46">
-        <v>-0.2784456140350877</v>
+        <v>-0.2784456140350878</v>
       </c>
       <c r="J46">
         <v>6.5</v>
@@ -2653,7 +2653,7 @@
         <v>-4.3684</v>
       </c>
       <c r="I53">
-        <v>0.958109649122807</v>
+        <v>0.9581096491228069</v>
       </c>
       <c r="J53">
         <v>6.5</v>
@@ -2881,7 +2881,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I59">
-        <v>-0.006774561403508789</v>
+        <v>-0.006774561403508753</v>
       </c>
       <c r="J59">
         <v>6.5</v>
@@ -3185,7 +3185,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I67">
-        <v>0.09611228070175441</v>
+        <v>0.0961122807017544</v>
       </c>
       <c r="J67">
         <v>6.5</v>
@@ -3261,7 +3261,7 @@
         <v>-5.9793</v>
       </c>
       <c r="I69">
-        <v>0.9138201754385965</v>
+        <v>0.9138201754385964</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3299,7 +3299,7 @@
         <v>-6.421</v>
       </c>
       <c r="I70">
-        <v>0.768890350877193</v>
+        <v>0.7688903508771929</v>
       </c>
       <c r="J70">
         <v>6.5</v>
@@ -3641,7 +3641,7 @@
         <v>-6.9307</v>
       </c>
       <c r="I79">
-        <v>0.2262622807017544</v>
+        <v>0.2262622807017543</v>
       </c>
       <c r="J79">
         <v>6.5</v>
@@ -3869,7 +3869,7 @@
         <v>-4.4856</v>
       </c>
       <c r="I85">
-        <v>0.4969324561403509</v>
+        <v>0.496932456140351</v>
       </c>
       <c r="J85">
         <v>6.5</v>
@@ -4249,7 +4249,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I95">
-        <v>0.03353596491228068</v>
+        <v>0.03353596491228069</v>
       </c>
       <c r="J95">
         <v>6.5</v>
@@ -4401,7 +4401,7 @@
         <v>-6.1071</v>
       </c>
       <c r="I99">
-        <v>0.06978508771929824</v>
+        <v>0.06978508771929823</v>
       </c>
       <c r="J99">
         <v>6.5</v>
@@ -4819,7 +4819,7 @@
         <v>-5.3412</v>
       </c>
       <c r="I110">
-        <v>0.3154666666666666</v>
+        <v>0.3154666666666667</v>
       </c>
       <c r="J110">
         <v>6.5</v>
@@ -4971,7 +4971,7 @@
         <v>-7.8913</v>
       </c>
       <c r="I114">
-        <v>0.1640561403508771</v>
+        <v>0.1640561403508772</v>
       </c>
       <c r="J114">
         <v>6.5</v>
@@ -5465,7 +5465,7 @@
         <v>-6.1057</v>
       </c>
       <c r="I127">
-        <v>0.7022105263157895</v>
+        <v>0.7022105263157894</v>
       </c>
       <c r="J127">
         <v>6.5</v>
@@ -5579,7 +5579,7 @@
         <v>-6.522</v>
       </c>
       <c r="I130">
-        <v>0.8603491228070175</v>
+        <v>0.8603491228070176</v>
       </c>
       <c r="J130">
         <v>6.5</v>
@@ -6301,7 +6301,7 @@
         <v>-7.7786</v>
       </c>
       <c r="I149">
-        <v>-0.3039491228070176</v>
+        <v>-0.3039491228070175</v>
       </c>
       <c r="J149">
         <v>6.5</v>
@@ -6605,7 +6605,7 @@
         <v>-6.0852</v>
       </c>
       <c r="I157">
-        <v>0.8567078947368421</v>
+        <v>0.8567078947368422</v>
       </c>
       <c r="J157">
         <v>6.5</v>
@@ -6833,7 +6833,7 @@
         <v>-5.4613</v>
       </c>
       <c r="I163">
-        <v>0.9106842105263159</v>
+        <v>0.9106842105263158</v>
       </c>
       <c r="J163">
         <v>6.5</v>
@@ -6909,7 +6909,7 @@
         <v>-8.1053</v>
       </c>
       <c r="I165">
-        <v>-0.1222131578947368</v>
+        <v>-0.1222131578947369</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7175,7 +7175,7 @@
         <v>-6.5046</v>
       </c>
       <c r="I172">
-        <v>0.7791377192982456</v>
+        <v>0.7791377192982457</v>
       </c>
       <c r="J172">
         <v>6.5</v>
@@ -7593,7 +7593,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I183">
-        <v>-0.05798157894736838</v>
+        <v>-0.0579815789473684</v>
       </c>
       <c r="J183">
         <v>6.5</v>
@@ -7859,7 +7859,7 @@
         <v>-4.7259</v>
       </c>
       <c r="I190">
-        <v>2.814910526315789</v>
+        <v>2.81491052631579</v>
       </c>
       <c r="J190">
         <v>6.5</v>
@@ -7973,7 +7973,7 @@
         <v>-4.9069</v>
       </c>
       <c r="I193">
-        <v>0.9718342105263158</v>
+        <v>0.9718342105263157</v>
       </c>
       <c r="J193">
         <v>6.5</v>
@@ -8277,7 +8277,7 @@
         <v>-4.9452</v>
       </c>
       <c r="I201">
-        <v>0.4920342105263157</v>
+        <v>0.4920342105263158</v>
       </c>
       <c r="J201">
         <v>6.5</v>
@@ -8315,7 +8315,7 @@
         <v>-7.4049</v>
       </c>
       <c r="I202">
-        <v>0.5309342105263157</v>
+        <v>0.5309342105263158</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8429,7 +8429,7 @@
         <v>-5.5515</v>
       </c>
       <c r="I205">
-        <v>0.3501815789473685</v>
+        <v>0.3501815789473684</v>
       </c>
       <c r="J205">
         <v>6.5</v>
@@ -8695,7 +8695,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I212">
-        <v>0.3845070175438597</v>
+        <v>0.3845070175438596</v>
       </c>
       <c r="J212">
         <v>6.5</v>
@@ -8733,7 +8733,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I213">
-        <v>0.6087508771929826</v>
+        <v>0.6087508771929824</v>
       </c>
       <c r="J213">
         <v>6.5</v>
@@ -9189,7 +9189,7 @@
         <v>-3.3104</v>
       </c>
       <c r="I225">
-        <v>0.8435719298245613</v>
+        <v>0.8435719298245615</v>
       </c>
       <c r="J225">
         <v>6.5</v>
@@ -9417,7 +9417,7 @@
         <v>-6.2062</v>
       </c>
       <c r="I231">
-        <v>0.3236368421052631</v>
+        <v>0.3236368421052632</v>
       </c>
       <c r="J231">
         <v>6.5</v>
@@ -9759,7 +9759,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I240">
-        <v>0.4163964912280703</v>
+        <v>0.4163964912280702</v>
       </c>
       <c r="J240">
         <v>6.5</v>
@@ -10139,7 +10139,7 @@
         <v>-7.0178</v>
       </c>
       <c r="I250">
-        <v>0.3055201754385965</v>
+        <v>0.3055201754385964</v>
       </c>
       <c r="J250">
         <v>6.5</v>
@@ -10291,7 +10291,7 @@
         <v>-6.6324</v>
       </c>
       <c r="I254">
-        <v>0.9322087719298247</v>
+        <v>0.9322087719298245</v>
       </c>
       <c r="J254">
         <v>6.5</v>
@@ -10633,7 +10633,7 @@
         <v>-5.9799</v>
       </c>
       <c r="I263">
-        <v>0.8239289473684211</v>
+        <v>0.823928947368421</v>
       </c>
       <c r="J263">
         <v>6.5</v>
@@ -10671,7 +10671,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I264">
-        <v>-0.05369473684210525</v>
+        <v>-0.05369473684210527</v>
       </c>
       <c r="J264">
         <v>6.5</v>
@@ -10747,7 +10747,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I266">
-        <v>0.09694385964912279</v>
+        <v>0.09694385964912282</v>
       </c>
       <c r="J266">
         <v>6.5</v>
@@ -11735,7 +11735,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I292">
-        <v>-0.08320087719298248</v>
+        <v>-0.08320087719298247</v>
       </c>
       <c r="J292">
         <v>6.5</v>
@@ -12381,7 +12381,7 @@
         <v>-6.4487</v>
       </c>
       <c r="I309">
-        <v>0.4012570175438597</v>
+        <v>0.4012570175438596</v>
       </c>
       <c r="J309">
         <v>6.5</v>
@@ -13293,7 +13293,7 @@
         <v>-5.792</v>
       </c>
       <c r="I333">
-        <v>0.8458587719298245</v>
+        <v>0.8458587719298246</v>
       </c>
       <c r="J333">
         <v>6.5</v>
@@ -13445,7 +13445,7 @@
         <v>-6.9831</v>
       </c>
       <c r="I337">
-        <v>0.2537947368421052</v>
+        <v>0.2537947368421053</v>
       </c>
       <c r="J337">
         <v>6.5</v>
@@ -13521,7 +13521,7 @@
         <v>-7.706</v>
       </c>
       <c r="I339">
-        <v>-0.0164666666666667</v>
+        <v>-0.01646666666666668</v>
       </c>
       <c r="J339">
         <v>6.5</v>
@@ -13635,7 +13635,7 @@
         <v>-6.4182</v>
       </c>
       <c r="I342">
-        <v>0.7823140350877194</v>
+        <v>0.7823140350877192</v>
       </c>
       <c r="J342">
         <v>6.5</v>
@@ -13787,7 +13787,7 @@
         <v>-5.956</v>
       </c>
       <c r="I346">
-        <v>1.530779824561404</v>
+        <v>1.530779824561403</v>
       </c>
       <c r="J346">
         <v>6.5</v>
@@ -14395,7 +14395,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I362">
-        <v>0.5621114035087719</v>
+        <v>0.562111403508772</v>
       </c>
       <c r="J362">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -867,7 +867,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I6">
-        <v>-0.057259649122807</v>
+        <v>-0.05725964912280698</v>
       </c>
       <c r="J6">
         <v>6.5</v>
@@ -905,7 +905,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I7">
-        <v>-0.04229736842105261</v>
+        <v>-0.04229736842105264</v>
       </c>
       <c r="J7">
         <v>6.5</v>
@@ -1247,7 +1247,7 @@
         <v>-4.5954</v>
       </c>
       <c r="I16">
-        <v>-0.1184026315789473</v>
+        <v>-0.1184026315789474</v>
       </c>
       <c r="J16">
         <v>6.5</v>
@@ -1399,7 +1399,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I20">
-        <v>-0.07766140350877193</v>
+        <v>-0.07766140350877192</v>
       </c>
       <c r="J20">
         <v>6.5</v>
@@ -1513,7 +1513,7 @@
         <v>-4.1055</v>
       </c>
       <c r="I23">
-        <v>0.4946271929824561</v>
+        <v>0.4946271929824562</v>
       </c>
       <c r="J23">
         <v>6.5</v>
@@ -1855,7 +1855,7 @@
         <v>-8.343400000000001</v>
       </c>
       <c r="I32">
-        <v>-0.8040798245614036</v>
+        <v>-0.8040798245614035</v>
       </c>
       <c r="J32">
         <v>6.5</v>
@@ -2083,7 +2083,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I38">
-        <v>-0.008549999999999988</v>
+        <v>-0.008550000000000006</v>
       </c>
       <c r="J38">
         <v>6.5</v>
@@ -2197,7 +2197,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I41">
-        <v>-0.0523719298245614</v>
+        <v>-0.05237192982456142</v>
       </c>
       <c r="J41">
         <v>6.5</v>
@@ -2235,7 +2235,7 @@
         <v>-5.7267</v>
       </c>
       <c r="I42">
-        <v>0.3732684210526315</v>
+        <v>0.3732684210526316</v>
       </c>
       <c r="J42">
         <v>6.5</v>
@@ -2387,7 +2387,7 @@
         <v>-6.5935</v>
       </c>
       <c r="I46">
-        <v>-0.2784456140350878</v>
+        <v>-0.2784456140350877</v>
       </c>
       <c r="J46">
         <v>6.5</v>
@@ -2767,7 +2767,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I56">
-        <v>1.477787719298246</v>
+        <v>1.477787719298245</v>
       </c>
       <c r="J56">
         <v>6.5</v>
@@ -2881,7 +2881,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I59">
-        <v>-0.006774561403508753</v>
+        <v>-0.006774561403508733</v>
       </c>
       <c r="J59">
         <v>6.5</v>
@@ -2957,7 +2957,7 @@
         <v>-5.2636</v>
       </c>
       <c r="I61">
-        <v>-0.09407280701754384</v>
+        <v>-0.09407280701754382</v>
       </c>
       <c r="J61">
         <v>6.5</v>
@@ -3185,7 +3185,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I67">
-        <v>0.0961122807017544</v>
+        <v>0.09611228070175443</v>
       </c>
       <c r="J67">
         <v>6.5</v>
@@ -3261,7 +3261,7 @@
         <v>-5.9793</v>
       </c>
       <c r="I69">
-        <v>0.9138201754385964</v>
+        <v>0.9138201754385965</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3527,7 +3527,7 @@
         <v>-6.9829</v>
       </c>
       <c r="I76">
-        <v>-0.6455096491228069</v>
+        <v>-0.6455096491228072</v>
       </c>
       <c r="J76">
         <v>6.5</v>
@@ -3641,7 +3641,7 @@
         <v>-6.9307</v>
       </c>
       <c r="I79">
-        <v>0.2262622807017543</v>
+        <v>0.2262622807017544</v>
       </c>
       <c r="J79">
         <v>6.5</v>
@@ -3983,7 +3983,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I88">
-        <v>-0.02176052631578945</v>
+        <v>-0.02176052631578946</v>
       </c>
       <c r="J88">
         <v>6.5</v>
@@ -4249,7 +4249,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I95">
-        <v>0.03353596491228069</v>
+        <v>0.03353596491228068</v>
       </c>
       <c r="J95">
         <v>6.5</v>
@@ -4401,7 +4401,7 @@
         <v>-6.1071</v>
       </c>
       <c r="I99">
-        <v>0.06978508771929823</v>
+        <v>0.06978508771929824</v>
       </c>
       <c r="J99">
         <v>6.5</v>
@@ -4933,7 +4933,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I113">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J113">
         <v>6.5</v>
@@ -4971,7 +4971,7 @@
         <v>-7.8913</v>
       </c>
       <c r="I114">
-        <v>0.1640561403508772</v>
+        <v>0.1640561403508771</v>
       </c>
       <c r="J114">
         <v>6.5</v>
@@ -5465,7 +5465,7 @@
         <v>-6.1057</v>
       </c>
       <c r="I127">
-        <v>0.7022105263157894</v>
+        <v>0.7022105263157895</v>
       </c>
       <c r="J127">
         <v>6.5</v>
@@ -5769,7 +5769,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I135">
-        <v>0.8890823008849557</v>
+        <v>0.8890823008849558</v>
       </c>
       <c r="J135">
         <v>6.5</v>
@@ -6035,7 +6035,7 @@
         <v>-7.3019</v>
       </c>
       <c r="I142">
-        <v>0.1687754385964913</v>
+        <v>0.1687754385964912</v>
       </c>
       <c r="J142">
         <v>6.5</v>
@@ -6073,7 +6073,7 @@
         <v>-5.5168</v>
       </c>
       <c r="I143">
-        <v>-0.2403578947368421</v>
+        <v>-0.2403578947368422</v>
       </c>
       <c r="J143">
         <v>6.5</v>
@@ -6111,7 +6111,7 @@
         <v>-7.2321</v>
       </c>
       <c r="I144">
-        <v>0.1916350877192982</v>
+        <v>0.1916350877192983</v>
       </c>
       <c r="J144">
         <v>6.5</v>
@@ -6605,7 +6605,7 @@
         <v>-6.0852</v>
       </c>
       <c r="I157">
-        <v>0.8567078947368422</v>
+        <v>0.8567078947368421</v>
       </c>
       <c r="J157">
         <v>6.5</v>
@@ -6909,7 +6909,7 @@
         <v>-8.1053</v>
       </c>
       <c r="I165">
-        <v>-0.1222131578947369</v>
+        <v>-0.1222131578947368</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7175,7 +7175,7 @@
         <v>-6.5046</v>
       </c>
       <c r="I172">
-        <v>0.7791377192982457</v>
+        <v>0.7791377192982456</v>
       </c>
       <c r="J172">
         <v>6.5</v>
@@ -7251,7 +7251,7 @@
         <v>-7.1203</v>
       </c>
       <c r="I174">
-        <v>0.9453815789473684</v>
+        <v>0.9453815789473685</v>
       </c>
       <c r="J174">
         <v>6.5</v>
@@ -7593,7 +7593,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I183">
-        <v>-0.0579815789473684</v>
+        <v>-0.05798157894736838</v>
       </c>
       <c r="J183">
         <v>6.5</v>
@@ -7669,7 +7669,7 @@
         <v>-5.6399</v>
       </c>
       <c r="I185">
-        <v>0.9184254385964912</v>
+        <v>0.9184254385964913</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -7973,7 +7973,7 @@
         <v>-4.9069</v>
       </c>
       <c r="I193">
-        <v>0.9718342105263157</v>
+        <v>0.9718342105263158</v>
       </c>
       <c r="J193">
         <v>6.5</v>
@@ -8315,7 +8315,7 @@
         <v>-7.4049</v>
       </c>
       <c r="I202">
-        <v>0.5309342105263158</v>
+        <v>0.5309342105263157</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8467,7 +8467,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I206">
-        <v>0.04088859649122804</v>
+        <v>0.04088859649122808</v>
       </c>
       <c r="J206">
         <v>6.5</v>
@@ -8543,7 +8543,7 @@
         <v>-6.532</v>
       </c>
       <c r="I208">
-        <v>0.01685877192982458</v>
+        <v>0.01685877192982455</v>
       </c>
       <c r="J208">
         <v>6.5</v>
@@ -8695,7 +8695,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I212">
-        <v>0.3845070175438596</v>
+        <v>0.3845070175438597</v>
       </c>
       <c r="J212">
         <v>6.5</v>
@@ -8733,7 +8733,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I213">
-        <v>0.6087508771929824</v>
+        <v>0.6087508771929826</v>
       </c>
       <c r="J213">
         <v>6.5</v>
@@ -9189,7 +9189,7 @@
         <v>-3.3104</v>
       </c>
       <c r="I225">
-        <v>0.8435719298245615</v>
+        <v>0.8435719298245613</v>
       </c>
       <c r="J225">
         <v>6.5</v>
@@ -9417,7 +9417,7 @@
         <v>-6.2062</v>
       </c>
       <c r="I231">
-        <v>0.3236368421052632</v>
+        <v>0.3236368421052631</v>
       </c>
       <c r="J231">
         <v>6.5</v>
@@ -9759,7 +9759,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I240">
-        <v>0.4163964912280702</v>
+        <v>0.4163964912280703</v>
       </c>
       <c r="J240">
         <v>6.5</v>
@@ -10139,7 +10139,7 @@
         <v>-7.0178</v>
       </c>
       <c r="I250">
-        <v>0.3055201754385964</v>
+        <v>0.3055201754385965</v>
       </c>
       <c r="J250">
         <v>6.5</v>
@@ -10633,7 +10633,7 @@
         <v>-5.9799</v>
       </c>
       <c r="I263">
-        <v>0.823928947368421</v>
+        <v>0.8239289473684211</v>
       </c>
       <c r="J263">
         <v>6.5</v>
@@ -10671,7 +10671,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I264">
-        <v>-0.05369473684210527</v>
+        <v>-0.05369473684210526</v>
       </c>
       <c r="J264">
         <v>6.5</v>
@@ -10747,7 +10747,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I266">
-        <v>0.09694385964912282</v>
+        <v>0.09694385964912279</v>
       </c>
       <c r="J266">
         <v>6.5</v>
@@ -11735,7 +11735,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I292">
-        <v>-0.08320087719298247</v>
+        <v>-0.08320087719298246</v>
       </c>
       <c r="J292">
         <v>6.5</v>
@@ -11963,7 +11963,7 @@
         <v>-5.9691</v>
       </c>
       <c r="I298">
-        <v>-0.09673684210526313</v>
+        <v>-0.09673684210526315</v>
       </c>
       <c r="J298">
         <v>6.5</v>
@@ -13293,7 +13293,7 @@
         <v>-5.792</v>
       </c>
       <c r="I333">
-        <v>0.8458587719298246</v>
+        <v>0.8458587719298245</v>
       </c>
       <c r="J333">
         <v>6.5</v>
@@ -13331,7 +13331,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I334">
-        <v>0.04960877192982455</v>
+        <v>0.04960877192982456</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -13369,7 +13369,7 @@
         <v>-6.0654</v>
       </c>
       <c r="I335">
-        <v>0.1482815789473684</v>
+        <v>0.1482815789473685</v>
       </c>
       <c r="J335">
         <v>6.5</v>
@@ -13521,7 +13521,7 @@
         <v>-7.706</v>
       </c>
       <c r="I339">
-        <v>-0.01646666666666668</v>
+        <v>-0.01646666666666671</v>
       </c>
       <c r="J339">
         <v>6.5</v>
@@ -13787,7 +13787,7 @@
         <v>-5.956</v>
       </c>
       <c r="I346">
-        <v>1.530779824561403</v>
+        <v>1.530779824561404</v>
       </c>
       <c r="J346">
         <v>6.5</v>
@@ -14319,7 +14319,7 @@
         <v>-6.3647</v>
       </c>
       <c r="I360">
-        <v>0.4170070175438597</v>
+        <v>0.4170070175438596</v>
       </c>
       <c r="J360">
         <v>6.5</v>
@@ -14395,7 +14395,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I362">
-        <v>0.562111403508772</v>
+        <v>0.5621114035087719</v>
       </c>
       <c r="J362">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -1371,7 +1371,7 @@
         <v>-3.2048</v>
       </c>
       <c r="I9">
-        <v>0.1313833333333334</v>
+        <v>0.1313833333333333</v>
       </c>
       <c r="J9">
         <v>6.5</v>
@@ -1409,7 +1409,7 @@
         <v>-24.3137</v>
       </c>
       <c r="I10">
-        <v>-0.3764089285714286</v>
+        <v>-0.3764089285714285</v>
       </c>
       <c r="J10">
         <v>6.5</v>
@@ -1789,7 +1789,7 @@
         <v>-3.2936</v>
       </c>
       <c r="I20">
-        <v>0.7082675438596492</v>
+        <v>0.7082675438596491</v>
       </c>
       <c r="J20">
         <v>6.5</v>
@@ -1827,7 +1827,7 @@
         <v>-7.6155</v>
       </c>
       <c r="I21">
-        <v>0.01529912280701757</v>
+        <v>0.01529912280701754</v>
       </c>
       <c r="J21">
         <v>6.5</v>
@@ -1865,7 +1865,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I22">
-        <v>0.130678947368421</v>
+        <v>0.1306789473684211</v>
       </c>
       <c r="J22">
         <v>6.5</v>
@@ -2017,7 +2017,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I26">
-        <v>-0.05725964912280702</v>
+        <v>-0.057259649122807</v>
       </c>
       <c r="J26">
         <v>6.5</v>
@@ -2549,7 +2549,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I40">
-        <v>-0.07766140350877195</v>
+        <v>-0.07766140350877192</v>
       </c>
       <c r="J40">
         <v>6.5</v>
@@ -2663,7 +2663,7 @@
         <v>-4.1055</v>
       </c>
       <c r="I43">
-        <v>0.4946271929824561</v>
+        <v>0.4946271929824562</v>
       </c>
       <c r="J43">
         <v>6.5</v>
@@ -2929,7 +2929,7 @@
         <v>-5.1686</v>
       </c>
       <c r="I50">
-        <v>0.06831403508771927</v>
+        <v>0.06831403508771933</v>
       </c>
       <c r="J50">
         <v>6.5</v>
@@ -3081,7 +3081,7 @@
         <v>-7.5421</v>
       </c>
       <c r="I54">
-        <v>-8.771929824517588E-06</v>
+        <v>-8.771929824560437E-06</v>
       </c>
       <c r="J54">
         <v>6.5</v>
@@ -3499,7 +3499,7 @@
         <v>-2.5972</v>
       </c>
       <c r="I65">
-        <v>2.138741228070176</v>
+        <v>2.138741228070175</v>
       </c>
       <c r="J65">
         <v>6.5</v>
@@ -3651,7 +3651,7 @@
         <v>-5.3978</v>
       </c>
       <c r="I69">
-        <v>0.7009289473684209</v>
+        <v>0.700928947368421</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3841,7 +3841,7 @@
         <v>-5.7396</v>
       </c>
       <c r="I74">
-        <v>0.2648552631578948</v>
+        <v>0.2648552631578947</v>
       </c>
       <c r="J74">
         <v>6.5</v>
@@ -4373,7 +4373,7 @@
         <v>-4.5504</v>
       </c>
       <c r="I88">
-        <v>0.86665</v>
+        <v>0.8666499999999999</v>
       </c>
       <c r="J88">
         <v>6.5</v>
@@ -4525,7 +4525,7 @@
         <v>-5.325</v>
       </c>
       <c r="I92">
-        <v>0.06181315789473681</v>
+        <v>0.06181315789473682</v>
       </c>
       <c r="J92">
         <v>6.5</v>
@@ -4563,7 +4563,7 @@
         <v>-5.5639</v>
       </c>
       <c r="I93">
-        <v>0.0316017543859649</v>
+        <v>0.03160175438596494</v>
       </c>
       <c r="J93">
         <v>6.5</v>
@@ -4601,7 +4601,7 @@
         <v>-4.9943</v>
       </c>
       <c r="I94">
-        <v>0.01033684210526313</v>
+        <v>0.01033684210526315</v>
       </c>
       <c r="J94">
         <v>6.5</v>
@@ -4639,7 +4639,7 @@
         <v>-5.2715</v>
       </c>
       <c r="I95">
-        <v>0.3232850877192983</v>
+        <v>0.3232850877192982</v>
       </c>
       <c r="J95">
         <v>6.5</v>
@@ -4753,7 +4753,7 @@
         <v>-5.5499</v>
       </c>
       <c r="I98">
-        <v>0.3972052631578947</v>
+        <v>0.3972052631578948</v>
       </c>
       <c r="J98">
         <v>6.5</v>
@@ -5057,7 +5057,7 @@
         <v>-3.7504</v>
       </c>
       <c r="I106">
-        <v>1.033949122807018</v>
+        <v>1.033949122807017</v>
       </c>
       <c r="J106">
         <v>6.5</v>
@@ -5133,7 +5133,7 @@
         <v>-4.9181</v>
       </c>
       <c r="I108">
-        <v>0.6396736842105263</v>
+        <v>0.6396736842105264</v>
       </c>
       <c r="J108">
         <v>6.5</v>
@@ -5209,7 +5209,7 @@
         <v>-7.6593</v>
       </c>
       <c r="I110">
-        <v>-0.304978947368421</v>
+        <v>-0.3049789473684211</v>
       </c>
       <c r="J110">
         <v>6.5</v>
@@ -5589,7 +5589,7 @@
         <v>-5.1558</v>
       </c>
       <c r="I120">
-        <v>-0.1938728070175439</v>
+        <v>-0.1938728070175438</v>
       </c>
       <c r="J120">
         <v>6.5</v>
@@ -5665,7 +5665,7 @@
         <v>-4.8973</v>
       </c>
       <c r="I122">
-        <v>0.3157789473684211</v>
+        <v>0.315778947368421</v>
       </c>
       <c r="J122">
         <v>6.5</v>
@@ -5817,7 +5817,7 @@
         <v>-4.8548</v>
       </c>
       <c r="I126">
-        <v>-0.02022920353982302</v>
+        <v>-0.02022920353982299</v>
       </c>
       <c r="J126">
         <v>6.5</v>
@@ -6045,7 +6045,7 @@
         <v>-4.7021</v>
       </c>
       <c r="I132">
-        <v>-0.04365350877192982</v>
+        <v>-0.04365350877192986</v>
       </c>
       <c r="J132">
         <v>6.5</v>
@@ -6083,7 +6083,7 @@
         <v>-4.7964</v>
       </c>
       <c r="I133">
-        <v>0.8078719298245615</v>
+        <v>0.8078719298245614</v>
       </c>
       <c r="J133">
         <v>6.5</v>
@@ -6159,7 +6159,7 @@
         <v>-5.6503</v>
       </c>
       <c r="I135">
-        <v>0.4333245614035087</v>
+        <v>0.4333245614035088</v>
       </c>
       <c r="J135">
         <v>6.5</v>
@@ -6197,7 +6197,7 @@
         <v>-4.3533</v>
       </c>
       <c r="I136">
-        <v>0.7331824561403509</v>
+        <v>0.7331824561403508</v>
       </c>
       <c r="J136">
         <v>6.5</v>
@@ -6235,7 +6235,7 @@
         <v>-6.3804</v>
       </c>
       <c r="I137">
-        <v>0.01184473684210525</v>
+        <v>0.01184473684210522</v>
       </c>
       <c r="J137">
         <v>6.5</v>
@@ -6653,7 +6653,7 @@
         <v>-4.2556</v>
       </c>
       <c r="I148">
-        <v>0.5377736842105264</v>
+        <v>0.5377736842105263</v>
       </c>
       <c r="J148">
         <v>6.5</v>
@@ -6805,7 +6805,7 @@
         <v>-4.8797</v>
       </c>
       <c r="I152">
-        <v>-0.225330701754386</v>
+        <v>-0.2253307017543859</v>
       </c>
       <c r="J152">
         <v>6.5</v>
@@ -7071,7 +7071,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I159">
-        <v>0.03470701754385962</v>
+        <v>0.0347070175438596</v>
       </c>
       <c r="J159">
         <v>6.5</v>
@@ -7109,7 +7109,7 @@
         <v>-5.1599</v>
       </c>
       <c r="I160">
-        <v>-0.4605105263157895</v>
+        <v>-0.4605105263157894</v>
       </c>
       <c r="J160">
         <v>6.5</v>
@@ -7147,7 +7147,7 @@
         <v>-5.9529</v>
       </c>
       <c r="I161">
-        <v>-0.4892543859649122</v>
+        <v>-0.4892543859649123</v>
       </c>
       <c r="J161">
         <v>6.5</v>
@@ -7299,7 +7299,7 @@
         <v>-4.6257</v>
       </c>
       <c r="I165">
-        <v>0.1766570175438596</v>
+        <v>0.1766570175438597</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7337,7 +7337,7 @@
         <v>-5.0848</v>
       </c>
       <c r="I166">
-        <v>-0.5323552631578947</v>
+        <v>-0.5323552631578948</v>
       </c>
       <c r="J166">
         <v>6.5</v>
@@ -7413,7 +7413,7 @@
         <v>-5.4305</v>
       </c>
       <c r="I168">
-        <v>0.3675763157894737</v>
+        <v>0.3675763157894736</v>
       </c>
       <c r="J168">
         <v>6.5</v>
@@ -7489,7 +7489,7 @@
         <v>-4.7969</v>
       </c>
       <c r="I170">
-        <v>0.2609666666666666</v>
+        <v>0.2609666666666667</v>
       </c>
       <c r="J170">
         <v>6.5</v>
@@ -7527,7 +7527,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I171">
-        <v>-0.04652807017543858</v>
+        <v>-0.04652807017543859</v>
       </c>
       <c r="J171">
         <v>6.5</v>
@@ -7831,7 +7831,7 @@
         <v>-8.343400000000001</v>
       </c>
       <c r="I179">
-        <v>-0.8040798245614036</v>
+        <v>-0.8040798245614035</v>
       </c>
       <c r="J179">
         <v>6.5</v>
@@ -8059,7 +8059,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I185">
-        <v>-0.008550000000000042</v>
+        <v>-0.008550000000000019</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -8325,7 +8325,7 @@
         <v>-4.7361</v>
       </c>
       <c r="I192">
-        <v>0.3821929824561404</v>
+        <v>0.3821929824561403</v>
       </c>
       <c r="J192">
         <v>6.5</v>
@@ -8629,7 +8629,7 @@
         <v>-4.3684</v>
       </c>
       <c r="I200">
-        <v>0.958109649122807</v>
+        <v>0.9581096491228069</v>
       </c>
       <c r="J200">
         <v>6.5</v>
@@ -8705,7 +8705,7 @@
         <v>-5.0406</v>
       </c>
       <c r="I202">
-        <v>-0.07873333333333331</v>
+        <v>-0.07873333333333334</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8743,7 +8743,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I203">
-        <v>1.477787719298245</v>
+        <v>1.477787719298246</v>
       </c>
       <c r="J203">
         <v>6.5</v>
@@ -9617,7 +9617,7 @@
         <v>-6.9307</v>
       </c>
       <c r="I226">
-        <v>0.2262622807017543</v>
+        <v>0.2262622807017544</v>
       </c>
       <c r="J226">
         <v>6.5</v>
@@ -9845,7 +9845,7 @@
         <v>-4.4856</v>
       </c>
       <c r="I232">
-        <v>0.496932456140351</v>
+        <v>0.4969324561403509</v>
       </c>
       <c r="J232">
         <v>6.5</v>
@@ -9921,7 +9921,7 @@
         <v>-4.5775</v>
       </c>
       <c r="I234">
-        <v>1.153189473684211</v>
+        <v>1.15318947368421</v>
       </c>
       <c r="J234">
         <v>6.5</v>
@@ -9959,7 +9959,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I235">
-        <v>-0.02176052631578949</v>
+        <v>-0.02176052631578944</v>
       </c>
       <c r="J235">
         <v>6.5</v>
@@ -10263,7 +10263,7 @@
         <v>-6.3915</v>
       </c>
       <c r="I243">
-        <v>0.3867263157894737</v>
+        <v>0.3867263157894736</v>
       </c>
       <c r="J243">
         <v>6.5</v>
@@ -10301,7 +10301,7 @@
         <v>-7.8256</v>
       </c>
       <c r="I244">
-        <v>0.03879035087719301</v>
+        <v>0.03879035087719299</v>
       </c>
       <c r="J244">
         <v>6.5</v>
@@ -10643,7 +10643,7 @@
         <v>-8.3277</v>
       </c>
       <c r="I253">
-        <v>-0.9198491228070176</v>
+        <v>-0.9198491228070175</v>
       </c>
       <c r="J253">
         <v>6.5</v>
@@ -10833,7 +10833,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I258">
-        <v>0.03353596491228066</v>
+        <v>0.0335359649122807</v>
       </c>
       <c r="J258">
         <v>6.5</v>
@@ -11365,7 +11365,7 @@
         <v>-6.9621</v>
       </c>
       <c r="I272">
-        <v>-0.2529184210526316</v>
+        <v>-0.2529184210526315</v>
       </c>
       <c r="J272">
         <v>6.5</v>
@@ -11517,7 +11517,7 @@
         <v>-5.205</v>
       </c>
       <c r="I276">
-        <v>0.5526894736842106</v>
+        <v>0.5526894736842105</v>
       </c>
       <c r="J276">
         <v>6.5</v>
@@ -11821,7 +11821,7 @@
         <v>-5.579</v>
       </c>
       <c r="I284">
-        <v>0.03944473684210525</v>
+        <v>0.03944473684210523</v>
       </c>
       <c r="J284">
         <v>6.5</v>
@@ -11897,7 +11897,7 @@
         <v>-4.7368</v>
       </c>
       <c r="I286">
-        <v>1.702028070175438</v>
+        <v>1.702028070175439</v>
       </c>
       <c r="J286">
         <v>6.5</v>
@@ -12353,7 +12353,7 @@
         <v>-5.9669</v>
       </c>
       <c r="I298">
-        <v>-0.177709649122807</v>
+        <v>-0.1777096491228071</v>
       </c>
       <c r="J298">
         <v>6.5</v>
@@ -12467,7 +12467,7 @@
         <v>-7.4805</v>
       </c>
       <c r="I301">
-        <v>0.08061228070175437</v>
+        <v>0.08061228070175436</v>
       </c>
       <c r="J301">
         <v>6.5</v>
@@ -12809,7 +12809,7 @@
         <v>-5.6215</v>
       </c>
       <c r="I310">
-        <v>0.9777149122807017</v>
+        <v>0.9777149122807018</v>
       </c>
       <c r="J310">
         <v>6.5</v>
@@ -13075,7 +13075,7 @@
         <v>-7.9728</v>
       </c>
       <c r="I317">
-        <v>0.8969166666666667</v>
+        <v>0.8969166666666666</v>
       </c>
       <c r="J317">
         <v>6.5</v>
@@ -13341,7 +13341,7 @@
         <v>-5.1407</v>
       </c>
       <c r="I324">
-        <v>0.2866377192982457</v>
+        <v>0.2866377192982456</v>
       </c>
       <c r="J324">
         <v>6.5</v>
@@ -13531,7 +13531,7 @@
         <v>-10.5468</v>
       </c>
       <c r="I329">
-        <v>-0.06476842105263156</v>
+        <v>-0.06476842105263157</v>
       </c>
       <c r="J329">
         <v>6.5</v>
@@ -13721,7 +13721,7 @@
         <v>-4.7487</v>
       </c>
       <c r="I334">
-        <v>-0.01714210526315789</v>
+        <v>-0.01714210526315788</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -13835,7 +13835,7 @@
         <v>-6.3764</v>
       </c>
       <c r="I337">
-        <v>0.8450508771929823</v>
+        <v>0.8450508771929826</v>
       </c>
       <c r="J337">
         <v>6.5</v>
@@ -14481,7 +14481,7 @@
         <v>-2.9022</v>
       </c>
       <c r="I354">
-        <v>1.770550877192982</v>
+        <v>1.770550877192983</v>
       </c>
       <c r="J354">
         <v>6.5</v>
@@ -14671,7 +14671,7 @@
         <v>-7.823</v>
       </c>
       <c r="I359">
-        <v>0.2566728070175438</v>
+        <v>0.2566728070175439</v>
       </c>
       <c r="J359">
         <v>6.5</v>
@@ -14785,7 +14785,7 @@
         <v>-5.1904</v>
       </c>
       <c r="I362">
-        <v>0.05131228070175436</v>
+        <v>0.05131228070175438</v>
       </c>
       <c r="J362">
         <v>6.5</v>
@@ -14937,7 +14937,7 @@
         <v>-4.4561</v>
       </c>
       <c r="I366">
-        <v>0.5883254385964913</v>
+        <v>0.5883254385964911</v>
       </c>
       <c r="J366">
         <v>6.5</v>
@@ -15393,7 +15393,7 @@
         <v>-5.1258</v>
       </c>
       <c r="I378">
-        <v>0.7531894736842105</v>
+        <v>0.7531894736842104</v>
       </c>
       <c r="J378">
         <v>6.5</v>
@@ -15849,7 +15849,7 @@
         <v>-4.5944</v>
       </c>
       <c r="I390">
-        <v>0.7309088495575222</v>
+        <v>0.7309088495575221</v>
       </c>
       <c r="J390">
         <v>6.5</v>
@@ -16153,7 +16153,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I398">
-        <v>0.8492342105263158</v>
+        <v>0.8492342105263159</v>
       </c>
       <c r="J398">
         <v>6.5</v>
@@ -16229,7 +16229,7 @@
         <v>-5.3412</v>
       </c>
       <c r="I400">
-        <v>0.3154666666666667</v>
+        <v>0.3154666666666666</v>
       </c>
       <c r="J400">
         <v>6.5</v>
@@ -16875,7 +16875,7 @@
         <v>-6.1057</v>
       </c>
       <c r="I417">
-        <v>0.7022105263157895</v>
+        <v>0.7022105263157894</v>
       </c>
       <c r="J417">
         <v>6.5</v>
@@ -17179,7 +17179,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I425">
-        <v>0.8890823008849558</v>
+        <v>0.8890823008849557</v>
       </c>
       <c r="J425">
         <v>6.5</v>
@@ -17521,7 +17521,7 @@
         <v>-7.2321</v>
       </c>
       <c r="I434">
-        <v>0.1916350877192983</v>
+        <v>0.1916350877192982</v>
       </c>
       <c r="J434">
         <v>6.5</v>
@@ -18015,7 +18015,7 @@
         <v>-6.0852</v>
       </c>
       <c r="I447">
-        <v>0.8567078947368421</v>
+        <v>0.8567078947368422</v>
       </c>
       <c r="J447">
         <v>6.5</v>
@@ -18243,7 +18243,7 @@
         <v>-5.4613</v>
       </c>
       <c r="I453">
-        <v>0.9106842105263159</v>
+        <v>0.9106842105263158</v>
       </c>
       <c r="J453">
         <v>6.5</v>
@@ -18623,7 +18623,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I463">
-        <v>-0.00590964912280705</v>
+        <v>-0.005909649122807043</v>
       </c>
       <c r="J463">
         <v>6.5</v>
@@ -18661,7 +18661,7 @@
         <v>-4.248</v>
       </c>
       <c r="I464">
-        <v>-0.2478280701754386</v>
+        <v>-0.2478280701754387</v>
       </c>
       <c r="J464">
         <v>6.5</v>
@@ -18889,7 +18889,7 @@
         <v>-4.958</v>
       </c>
       <c r="I470">
-        <v>0.01515087719298248</v>
+        <v>0.01515087719298249</v>
       </c>
       <c r="J470">
         <v>6.5</v>
@@ -19497,7 +19497,7 @@
         <v>-5.0702</v>
       </c>
       <c r="I486">
-        <v>0.4123807017543859</v>
+        <v>0.412380701754386</v>
       </c>
       <c r="J486">
         <v>6.5</v>
@@ -19535,7 +19535,7 @@
         <v>-7.0157</v>
       </c>
       <c r="I487">
-        <v>0.9124140350877193</v>
+        <v>0.9124140350877192</v>
       </c>
       <c r="J487">
         <v>6.5</v>
@@ -19725,7 +19725,7 @@
         <v>-5.1068</v>
       </c>
       <c r="I492">
-        <v>0.0981026315789474</v>
+        <v>0.09810263157894737</v>
       </c>
       <c r="J492">
         <v>6.5</v>
@@ -20257,7 +20257,7 @@
         <v>-6.9126</v>
       </c>
       <c r="I506">
-        <v>-0.007017543859649133</v>
+        <v>-0.007017543859649098</v>
       </c>
       <c r="J506">
         <v>6.5</v>
@@ -20523,7 +20523,7 @@
         <v>-7.7903</v>
       </c>
       <c r="I513">
-        <v>0.6595526315789474</v>
+        <v>0.6595526315789473</v>
       </c>
       <c r="J513">
         <v>6.5</v>
@@ -20675,7 +20675,7 @@
         <v>-8.1221</v>
       </c>
       <c r="I517">
-        <v>0.3949614035087719</v>
+        <v>0.394961403508772</v>
       </c>
       <c r="J517">
         <v>6.5</v>
@@ -20865,7 +20865,7 @@
         <v>-5.2765</v>
       </c>
       <c r="I522">
-        <v>-0.04416403508771927</v>
+        <v>-0.04416403508771931</v>
       </c>
       <c r="J522">
         <v>6.5</v>
@@ -21093,7 +21093,7 @@
         <v>-5.7272</v>
       </c>
       <c r="I528">
-        <v>-0.178140350877193</v>
+        <v>-0.1781403508771931</v>
       </c>
       <c r="J528">
         <v>6.5</v>
@@ -21397,7 +21397,7 @@
         <v>-5.1151</v>
       </c>
       <c r="I536">
-        <v>0.09153333333333331</v>
+        <v>0.0915333333333333</v>
       </c>
       <c r="J536">
         <v>6.5</v>
@@ -21511,7 +21511,7 @@
         <v>-6.0147</v>
       </c>
       <c r="I539">
-        <v>0.631080701754386</v>
+        <v>0.6310807017543859</v>
       </c>
       <c r="J539">
         <v>6.5</v>
@@ -21587,7 +21587,7 @@
         <v>-7.8784</v>
       </c>
       <c r="I541">
-        <v>-0.1674350877192982</v>
+        <v>-0.1674350877192983</v>
       </c>
       <c r="J541">
         <v>6.5</v>
@@ -21701,7 +21701,7 @@
         <v>-7.3353</v>
       </c>
       <c r="I544">
-        <v>-0.631270796460177</v>
+        <v>-0.6312707964601769</v>
       </c>
       <c r="J544">
         <v>6.5</v>
@@ -21815,7 +21815,7 @@
         <v>-6.3641</v>
       </c>
       <c r="I547">
-        <v>0.8495912280701754</v>
+        <v>0.8495912280701755</v>
       </c>
       <c r="J547">
         <v>6.5</v>
@@ -22005,7 +22005,7 @@
         <v>-5.5816</v>
       </c>
       <c r="I552">
-        <v>0.09724473684210527</v>
+        <v>0.09724473684210529</v>
       </c>
       <c r="J552">
         <v>6.5</v>
@@ -22347,7 +22347,7 @@
         <v>-6.8291</v>
       </c>
       <c r="I561">
-        <v>0.9898657894736841</v>
+        <v>0.9898657894736842</v>
       </c>
       <c r="J561">
         <v>6.5</v>
@@ -22499,7 +22499,7 @@
         <v>-8.0747</v>
       </c>
       <c r="I565">
-        <v>0.5883105263157895</v>
+        <v>0.5883105263157894</v>
       </c>
       <c r="J565">
         <v>6.5</v>
@@ -23373,7 +23373,7 @@
         <v>-5.4435</v>
       </c>
       <c r="I588">
-        <v>0.7361754385964913</v>
+        <v>0.7361754385964911</v>
       </c>
       <c r="J588">
         <v>6.5</v>
@@ -23487,7 +23487,7 @@
         <v>-6.9653</v>
       </c>
       <c r="I591">
-        <v>-0.02084210526315788</v>
+        <v>-0.02084210526315791</v>
       </c>
       <c r="J591">
         <v>6.5</v>
@@ -23525,7 +23525,7 @@
         <v>-4.5308</v>
       </c>
       <c r="I592">
-        <v>0.887792105263158</v>
+        <v>0.8877921052631579</v>
       </c>
       <c r="J592">
         <v>6.5</v>
@@ -23791,7 +23791,7 @@
         <v>-6.5046</v>
       </c>
       <c r="I599">
-        <v>0.7791377192982457</v>
+        <v>0.7791377192982456</v>
       </c>
       <c r="J599">
         <v>6.5</v>
@@ -24209,7 +24209,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I610">
-        <v>-0.05798157894736838</v>
+        <v>-0.05798157894736837</v>
       </c>
       <c r="J610">
         <v>6.5</v>
@@ -24931,7 +24931,7 @@
         <v>-7.4049</v>
       </c>
       <c r="I629">
-        <v>0.5309342105263158</v>
+        <v>0.5309342105263157</v>
       </c>
       <c r="J629">
         <v>6.5</v>
@@ -25083,7 +25083,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I633">
-        <v>0.04088859649122804</v>
+        <v>0.04088859649122808</v>
       </c>
       <c r="J633">
         <v>6.5</v>
@@ -25121,7 +25121,7 @@
         <v>-5.6411</v>
       </c>
       <c r="I634">
-        <v>0.6434964912280703</v>
+        <v>0.6434964912280702</v>
       </c>
       <c r="J634">
         <v>6.5</v>
@@ -25159,7 +25159,7 @@
         <v>-6.532</v>
       </c>
       <c r="I635">
-        <v>0.01685877192982458</v>
+        <v>0.01685877192982452</v>
       </c>
       <c r="J635">
         <v>6.5</v>
@@ -25349,7 +25349,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I640">
-        <v>0.6087508771929826</v>
+        <v>0.6087508771929824</v>
       </c>
       <c r="J640">
         <v>6.5</v>
@@ -25615,7 +25615,7 @@
         <v>-7.8297</v>
       </c>
       <c r="I647">
-        <v>0.3773359649122808</v>
+        <v>0.3773359649122807</v>
       </c>
       <c r="J647">
         <v>6.5</v>
@@ -25729,7 +25729,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I650">
-        <v>-0.2874561403508771</v>
+        <v>-0.2874561403508772</v>
       </c>
       <c r="J650">
         <v>6.5</v>
@@ -26033,7 +26033,7 @@
         <v>-6.2062</v>
       </c>
       <c r="I658">
-        <v>0.3236368421052632</v>
+        <v>0.3236368421052631</v>
       </c>
       <c r="J658">
         <v>6.5</v>
@@ -26489,7 +26489,7 @@
         <v>-7.7299</v>
       </c>
       <c r="I670">
-        <v>0.337980701754386</v>
+        <v>0.3379807017543859</v>
       </c>
       <c r="J670">
         <v>6.5</v>
@@ -26565,7 +26565,7 @@
         <v>-8.907500000000001</v>
       </c>
       <c r="I672">
-        <v>0.05063859649122811</v>
+        <v>0.05063859649122808</v>
       </c>
       <c r="J672">
         <v>6.5</v>
@@ -26603,7 +26603,7 @@
         <v>-9.5877</v>
       </c>
       <c r="I673">
-        <v>-0.7989043859649122</v>
+        <v>-0.7989043859649123</v>
       </c>
       <c r="J673">
         <v>6.5</v>
@@ -27401,7 +27401,7 @@
         <v>-6.3524</v>
       </c>
       <c r="I694">
-        <v>-0.1134263157894737</v>
+        <v>-0.1134263157894736</v>
       </c>
       <c r="J694">
         <v>6.5</v>
@@ -27439,7 +27439,7 @@
         <v>-5.7765</v>
       </c>
       <c r="I695">
-        <v>2.461089473684211</v>
+        <v>2.46108947368421</v>
       </c>
       <c r="J695">
         <v>6.5</v>
@@ -28047,7 +28047,7 @@
         <v>-6.0046</v>
       </c>
       <c r="I711">
-        <v>1.319487719298245</v>
+        <v>1.319487719298246</v>
       </c>
       <c r="J711">
         <v>6.5</v>
@@ -28275,7 +28275,7 @@
         <v>-5.1711</v>
       </c>
       <c r="I717">
-        <v>0.7814701754385964</v>
+        <v>0.7814701754385965</v>
       </c>
       <c r="J717">
         <v>6.5</v>
@@ -28427,7 +28427,7 @@
         <v>-5.9914</v>
       </c>
       <c r="I721">
-        <v>0.6895745614035088</v>
+        <v>0.6895745614035087</v>
       </c>
       <c r="J721">
         <v>6.5</v>
@@ -28503,7 +28503,7 @@
         <v>-6.4442</v>
       </c>
       <c r="I723">
-        <v>0.7272859649122807</v>
+        <v>0.7272859649122806</v>
       </c>
       <c r="J723">
         <v>6.5</v>
@@ -28693,7 +28693,7 @@
         <v>-4.1714</v>
       </c>
       <c r="I728">
-        <v>0.03119473684210524</v>
+        <v>0.03119473684210523</v>
       </c>
       <c r="J728">
         <v>6.5</v>
@@ -29111,7 +29111,7 @@
         <v>-5.2556</v>
       </c>
       <c r="I739">
-        <v>0.07302192982456138</v>
+        <v>0.07302192982456139</v>
       </c>
       <c r="J739">
         <v>6.5</v>
@@ -29491,7 +29491,7 @@
         <v>-6.2194</v>
       </c>
       <c r="I749">
-        <v>0.4190657894736843</v>
+        <v>0.4190657894736842</v>
       </c>
       <c r="J749">
         <v>6.5</v>
@@ -29757,7 +29757,7 @@
         <v>-7.4388</v>
       </c>
       <c r="I756">
-        <v>0.8952345132743363</v>
+        <v>0.8952345132743362</v>
       </c>
       <c r="J756">
         <v>6.5</v>
@@ -31581,7 +31581,7 @@
         <v>-7.0178</v>
       </c>
       <c r="I804">
-        <v>0.3055201754385965</v>
+        <v>0.3055201754385964</v>
       </c>
       <c r="J804">
         <v>6.5</v>
@@ -32113,7 +32113,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I818">
-        <v>-0.05369473684210525</v>
+        <v>-0.05369473684210526</v>
       </c>
       <c r="J818">
         <v>6.5</v>
@@ -32189,7 +32189,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I820">
-        <v>0.09694385964912278</v>
+        <v>0.09694385964912279</v>
       </c>
       <c r="J820">
         <v>6.5</v>
@@ -33481,7 +33481,7 @@
         <v>-6.8676</v>
       </c>
       <c r="I854">
-        <v>-0.05854690265486728</v>
+        <v>-0.05854690265486726</v>
       </c>
       <c r="J854">
         <v>6.5</v>
@@ -33595,7 +33595,7 @@
         <v>-5.1365</v>
       </c>
       <c r="I857">
-        <v>0.3506315789473684</v>
+        <v>0.3506315789473683</v>
       </c>
       <c r="J857">
         <v>6.5</v>
@@ -33975,7 +33975,7 @@
         <v>-5.9705</v>
       </c>
       <c r="I867">
-        <v>0.8947973684210526</v>
+        <v>0.8947973684210525</v>
       </c>
       <c r="J867">
         <v>6.5</v>
@@ -34127,7 +34127,7 @@
         <v>-5.7904</v>
       </c>
       <c r="I871">
-        <v>-0.01008245614035086</v>
+        <v>-0.01008245614035088</v>
       </c>
       <c r="J871">
         <v>6.5</v>
@@ -34355,7 +34355,7 @@
         <v>-5.1564</v>
       </c>
       <c r="I877">
-        <v>1.370497368421052</v>
+        <v>1.370497368421053</v>
       </c>
       <c r="J877">
         <v>6.5</v>
@@ -34431,7 +34431,7 @@
         <v>-7.0621</v>
       </c>
       <c r="I879">
-        <v>-0.6554561403508773</v>
+        <v>-0.6554561403508772</v>
       </c>
       <c r="J879">
         <v>6.5</v>
@@ -34773,7 +34773,7 @@
         <v>-5.5022</v>
       </c>
       <c r="I888">
-        <v>0.4009543859649123</v>
+        <v>0.4009543859649122</v>
       </c>
       <c r="J888">
         <v>6.5</v>
@@ -34963,7 +34963,7 @@
         <v>-6.183</v>
       </c>
       <c r="I893">
-        <v>0.771830701754386</v>
+        <v>0.7718307017543861</v>
       </c>
       <c r="J893">
         <v>6.5</v>
@@ -35761,7 +35761,7 @@
         <v>-5.5058</v>
       </c>
       <c r="I914">
-        <v>0.6981254385964913</v>
+        <v>0.6981254385964912</v>
       </c>
       <c r="J914">
         <v>6.5</v>
@@ -36521,7 +36521,7 @@
         <v>-5.8651</v>
       </c>
       <c r="I934">
-        <v>0.09259035087719296</v>
+        <v>0.09259035087719297</v>
       </c>
       <c r="J934">
         <v>6.5</v>
@@ -36673,7 +36673,7 @@
         <v>-4.314</v>
       </c>
       <c r="I938">
-        <v>-0.03864649122807018</v>
+        <v>-0.03864649122807017</v>
       </c>
       <c r="J938">
         <v>6.5</v>
@@ -37091,7 +37091,7 @@
         <v>-5.5354</v>
       </c>
       <c r="I949">
-        <v>0.2661078947368421</v>
+        <v>0.266107894736842</v>
       </c>
       <c r="J949">
         <v>6.5</v>
@@ -37129,7 +37129,7 @@
         <v>-6.2272</v>
       </c>
       <c r="I950">
-        <v>0.04605309734513274</v>
+        <v>0.04605309734513276</v>
       </c>
       <c r="J950">
         <v>6.5</v>
@@ -37661,7 +37661,7 @@
         <v>-5.9172</v>
       </c>
       <c r="I964">
-        <v>0.339588596491228</v>
+        <v>0.3395885964912281</v>
       </c>
       <c r="J964">
         <v>6.5</v>
@@ -38649,7 +38649,7 @@
         <v>-5.9258</v>
       </c>
       <c r="I990">
-        <v>0.6400684210526315</v>
+        <v>0.6400684210526317</v>
       </c>
       <c r="J990">
         <v>6.5</v>
@@ -39865,7 +39865,7 @@
         <v>-7.706</v>
       </c>
       <c r="I1022">
-        <v>-0.0164666666666667</v>
+        <v>-0.01646666666666671</v>
       </c>
       <c r="J1022">
         <v>6.5</v>
@@ -40283,7 +40283,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I1033">
-        <v>0.01259649122807017</v>
+        <v>0.01259649122807015</v>
       </c>
       <c r="J1033">
         <v>6.5</v>
@@ -40739,7 +40739,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I1045">
-        <v>0.562111403508772</v>
+        <v>0.5621114035087719</v>
       </c>
       <c r="J1045">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -1371,7 +1371,7 @@
         <v>-3.2048</v>
       </c>
       <c r="I9">
-        <v>0.1313833333333333</v>
+        <v>0.1313833333333334</v>
       </c>
       <c r="J9">
         <v>6.5</v>
@@ -1409,7 +1409,7 @@
         <v>-24.3137</v>
       </c>
       <c r="I10">
-        <v>-0.3764089285714285</v>
+        <v>-0.3764089285714286</v>
       </c>
       <c r="J10">
         <v>6.5</v>
@@ -1865,7 +1865,7 @@
         <v>-3.1139</v>
       </c>
       <c r="I22">
-        <v>0.1306789473684211</v>
+        <v>0.130678947368421</v>
       </c>
       <c r="J22">
         <v>6.5</v>
@@ -2017,7 +2017,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I26">
-        <v>-0.057259649122807</v>
+        <v>-0.05725964912280702</v>
       </c>
       <c r="J26">
         <v>6.5</v>
@@ -2055,7 +2055,7 @@
         <v>-3.4499</v>
       </c>
       <c r="I27">
-        <v>-0.04229736842105265</v>
+        <v>-0.04229736842105263</v>
       </c>
       <c r="J27">
         <v>6.5</v>
@@ -2549,7 +2549,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I40">
-        <v>-0.07766140350877192</v>
+        <v>-0.07766140350877193</v>
       </c>
       <c r="J40">
         <v>6.5</v>
@@ -2663,7 +2663,7 @@
         <v>-4.1055</v>
       </c>
       <c r="I43">
-        <v>0.4946271929824562</v>
+        <v>0.4946271929824561</v>
       </c>
       <c r="J43">
         <v>6.5</v>
@@ -3081,7 +3081,7 @@
         <v>-7.5421</v>
       </c>
       <c r="I54">
-        <v>-8.771929824560437E-06</v>
+        <v>-8.7719298245171E-06</v>
       </c>
       <c r="J54">
         <v>6.5</v>
@@ -3651,7 +3651,7 @@
         <v>-5.3978</v>
       </c>
       <c r="I69">
-        <v>0.700928947368421</v>
+        <v>0.7009289473684209</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3841,7 +3841,7 @@
         <v>-5.7396</v>
       </c>
       <c r="I74">
-        <v>0.2648552631578947</v>
+        <v>0.2648552631578948</v>
       </c>
       <c r="J74">
         <v>6.5</v>
@@ -3917,7 +3917,7 @@
         <v>-7.1749</v>
       </c>
       <c r="I76">
-        <v>0.3746035087719298</v>
+        <v>0.3746035087719299</v>
       </c>
       <c r="J76">
         <v>6.5</v>
@@ -4259,7 +4259,7 @@
         <v>-5.5616</v>
       </c>
       <c r="I85">
-        <v>-0.00570877192982456</v>
+        <v>-0.005708771929824567</v>
       </c>
       <c r="J85">
         <v>6.5</v>
@@ -4525,7 +4525,7 @@
         <v>-5.325</v>
       </c>
       <c r="I92">
-        <v>0.06181315789473682</v>
+        <v>0.06181315789473684</v>
       </c>
       <c r="J92">
         <v>6.5</v>
@@ -4563,7 +4563,7 @@
         <v>-5.5639</v>
       </c>
       <c r="I93">
-        <v>0.03160175438596494</v>
+        <v>0.0316017543859649</v>
       </c>
       <c r="J93">
         <v>6.5</v>
@@ -4639,7 +4639,7 @@
         <v>-5.2715</v>
       </c>
       <c r="I95">
-        <v>0.3232850877192982</v>
+        <v>0.3232850877192983</v>
       </c>
       <c r="J95">
         <v>6.5</v>
@@ -4753,7 +4753,7 @@
         <v>-5.5499</v>
       </c>
       <c r="I98">
-        <v>0.3972052631578948</v>
+        <v>0.3972052631578947</v>
       </c>
       <c r="J98">
         <v>6.5</v>
@@ -5019,7 +5019,7 @@
         <v>-5.7006</v>
       </c>
       <c r="I105">
-        <v>-0.2644166666666667</v>
+        <v>-0.2644166666666666</v>
       </c>
       <c r="J105">
         <v>6.5</v>
@@ -5133,7 +5133,7 @@
         <v>-4.9181</v>
       </c>
       <c r="I108">
-        <v>0.6396736842105264</v>
+        <v>0.6396736842105263</v>
       </c>
       <c r="J108">
         <v>6.5</v>
@@ -5209,7 +5209,7 @@
         <v>-7.6593</v>
       </c>
       <c r="I110">
-        <v>-0.3049789473684211</v>
+        <v>-0.304978947368421</v>
       </c>
       <c r="J110">
         <v>6.5</v>
@@ -5323,7 +5323,7 @@
         <v>-6.1612</v>
       </c>
       <c r="I113">
-        <v>0.1059350877192983</v>
+        <v>0.1059350877192982</v>
       </c>
       <c r="J113">
         <v>6.5</v>
@@ -5551,7 +5551,7 @@
         <v>-4.9268</v>
       </c>
       <c r="I119">
-        <v>0.1207350877192982</v>
+        <v>0.1207350877192983</v>
       </c>
       <c r="J119">
         <v>6.5</v>
@@ -5665,7 +5665,7 @@
         <v>-4.8973</v>
       </c>
       <c r="I122">
-        <v>0.315778947368421</v>
+        <v>0.3157789473684211</v>
       </c>
       <c r="J122">
         <v>6.5</v>
@@ -5817,7 +5817,7 @@
         <v>-4.8548</v>
       </c>
       <c r="I126">
-        <v>-0.02022920353982299</v>
+        <v>-0.02022920353982301</v>
       </c>
       <c r="J126">
         <v>6.5</v>
@@ -6045,7 +6045,7 @@
         <v>-4.7021</v>
       </c>
       <c r="I132">
-        <v>-0.04365350877192986</v>
+        <v>-0.04365350877192985</v>
       </c>
       <c r="J132">
         <v>6.5</v>
@@ -6121,7 +6121,7 @@
         <v>-5.4098</v>
       </c>
       <c r="I134">
-        <v>-0.2065377192982456</v>
+        <v>-0.2065377192982457</v>
       </c>
       <c r="J134">
         <v>6.5</v>
@@ -6159,7 +6159,7 @@
         <v>-5.6503</v>
       </c>
       <c r="I135">
-        <v>0.4333245614035088</v>
+        <v>0.4333245614035087</v>
       </c>
       <c r="J135">
         <v>6.5</v>
@@ -6235,7 +6235,7 @@
         <v>-6.3804</v>
       </c>
       <c r="I137">
-        <v>0.01184473684210522</v>
+        <v>0.01184473684210523</v>
       </c>
       <c r="J137">
         <v>6.5</v>
@@ -6349,7 +6349,7 @@
         <v>-5.4954</v>
       </c>
       <c r="I140">
-        <v>-0.07092123893805306</v>
+        <v>-0.07092123893805304</v>
       </c>
       <c r="J140">
         <v>6.5</v>
@@ -6653,7 +6653,7 @@
         <v>-4.2556</v>
       </c>
       <c r="I148">
-        <v>0.5377736842105263</v>
+        <v>0.5377736842105264</v>
       </c>
       <c r="J148">
         <v>6.5</v>
@@ -6767,7 +6767,7 @@
         <v>-5.5488</v>
       </c>
       <c r="I151">
-        <v>-0.09169736842105261</v>
+        <v>-0.09169736842105258</v>
       </c>
       <c r="J151">
         <v>6.5</v>
@@ -6805,7 +6805,7 @@
         <v>-4.8797</v>
       </c>
       <c r="I152">
-        <v>-0.2253307017543859</v>
+        <v>-0.225330701754386</v>
       </c>
       <c r="J152">
         <v>6.5</v>
@@ -7071,7 +7071,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I159">
-        <v>0.0347070175438596</v>
+        <v>0.03470701754385963</v>
       </c>
       <c r="J159">
         <v>6.5</v>
@@ -7299,7 +7299,7 @@
         <v>-4.6257</v>
       </c>
       <c r="I165">
-        <v>0.1766570175438597</v>
+        <v>0.1766570175438596</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7413,7 +7413,7 @@
         <v>-5.4305</v>
       </c>
       <c r="I168">
-        <v>0.3675763157894736</v>
+        <v>0.3675763157894737</v>
       </c>
       <c r="J168">
         <v>6.5</v>
@@ -7451,7 +7451,7 @@
         <v>-4.7737</v>
       </c>
       <c r="I169">
-        <v>0.2246771929824561</v>
+        <v>0.2246771929824562</v>
       </c>
       <c r="J169">
         <v>6.5</v>
@@ -7489,7 +7489,7 @@
         <v>-4.7969</v>
       </c>
       <c r="I170">
-        <v>0.2609666666666667</v>
+        <v>0.2609666666666666</v>
       </c>
       <c r="J170">
         <v>6.5</v>
@@ -7527,7 +7527,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I171">
-        <v>-0.04652807017543859</v>
+        <v>-0.04652807017543861</v>
       </c>
       <c r="J171">
         <v>6.5</v>
@@ -8059,7 +8059,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I185">
-        <v>-0.008550000000000019</v>
+        <v>-0.008550000000000035</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -8173,7 +8173,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I188">
-        <v>-0.0523719298245614</v>
+        <v>-0.05237192982456141</v>
       </c>
       <c r="J188">
         <v>6.5</v>
@@ -8629,7 +8629,7 @@
         <v>-4.3684</v>
       </c>
       <c r="I200">
-        <v>0.9581096491228069</v>
+        <v>0.958109649122807</v>
       </c>
       <c r="J200">
         <v>6.5</v>
@@ -8705,7 +8705,7 @@
         <v>-5.0406</v>
       </c>
       <c r="I202">
-        <v>-0.07873333333333334</v>
+        <v>-0.07873333333333332</v>
       </c>
       <c r="J202">
         <v>6.5</v>
@@ -8857,7 +8857,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I206">
-        <v>-0.006774561403508784</v>
+        <v>-0.006774561403508753</v>
       </c>
       <c r="J206">
         <v>6.5</v>
@@ -9845,7 +9845,7 @@
         <v>-4.4856</v>
       </c>
       <c r="I232">
-        <v>0.4969324561403509</v>
+        <v>0.496932456140351</v>
       </c>
       <c r="J232">
         <v>6.5</v>
@@ -9921,7 +9921,7 @@
         <v>-4.5775</v>
       </c>
       <c r="I234">
-        <v>1.15318947368421</v>
+        <v>1.153189473684211</v>
       </c>
       <c r="J234">
         <v>6.5</v>
@@ -9959,7 +9959,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I235">
-        <v>-0.02176052631578944</v>
+        <v>-0.02176052631578946</v>
       </c>
       <c r="J235">
         <v>6.5</v>
@@ -10263,7 +10263,7 @@
         <v>-6.3915</v>
       </c>
       <c r="I243">
-        <v>0.3867263157894736</v>
+        <v>0.3867263157894737</v>
       </c>
       <c r="J243">
         <v>6.5</v>
@@ -10301,7 +10301,7 @@
         <v>-7.8256</v>
       </c>
       <c r="I244">
-        <v>0.03879035087719299</v>
+        <v>0.038790350877193</v>
       </c>
       <c r="J244">
         <v>6.5</v>
@@ -10643,7 +10643,7 @@
         <v>-8.3277</v>
       </c>
       <c r="I253">
-        <v>-0.9198491228070175</v>
+        <v>-0.9198491228070176</v>
       </c>
       <c r="J253">
         <v>6.5</v>
@@ -10757,7 +10757,7 @@
         <v>-4.0971</v>
       </c>
       <c r="I256">
-        <v>0.5978482456140352</v>
+        <v>0.597848245614035</v>
       </c>
       <c r="J256">
         <v>6.5</v>
@@ -10833,7 +10833,7 @@
         <v>-5.0645</v>
       </c>
       <c r="I258">
-        <v>0.0335359649122807</v>
+        <v>0.03353596491228068</v>
       </c>
       <c r="J258">
         <v>6.5</v>
@@ -10871,7 +10871,7 @@
         <v>-6.9585</v>
       </c>
       <c r="I259">
-        <v>-1.168720175438597</v>
+        <v>-1.168720175438596</v>
       </c>
       <c r="J259">
         <v>6.5</v>
@@ -11365,7 +11365,7 @@
         <v>-6.9621</v>
       </c>
       <c r="I272">
-        <v>-0.2529184210526315</v>
+        <v>-0.2529184210526316</v>
       </c>
       <c r="J272">
         <v>6.5</v>
@@ -11479,7 +11479,7 @@
         <v>-9.9345</v>
       </c>
       <c r="I275">
-        <v>-0.09860000000000001</v>
+        <v>-0.09860000000000002</v>
       </c>
       <c r="J275">
         <v>6.5</v>
@@ -11821,7 +11821,7 @@
         <v>-5.579</v>
       </c>
       <c r="I284">
-        <v>0.03944473684210523</v>
+        <v>0.03944473684210526</v>
       </c>
       <c r="J284">
         <v>6.5</v>
@@ -12353,7 +12353,7 @@
         <v>-5.9669</v>
       </c>
       <c r="I298">
-        <v>-0.1777096491228071</v>
+        <v>-0.177709649122807</v>
       </c>
       <c r="J298">
         <v>6.5</v>
@@ -12467,7 +12467,7 @@
         <v>-7.4805</v>
       </c>
       <c r="I301">
-        <v>0.08061228070175436</v>
+        <v>0.08061228070175437</v>
       </c>
       <c r="J301">
         <v>6.5</v>
@@ -12809,7 +12809,7 @@
         <v>-5.6215</v>
       </c>
       <c r="I310">
-        <v>0.9777149122807018</v>
+        <v>0.9777149122807017</v>
       </c>
       <c r="J310">
         <v>6.5</v>
@@ -13341,7 +13341,7 @@
         <v>-5.1407</v>
       </c>
       <c r="I324">
-        <v>0.2866377192982456</v>
+        <v>0.2866377192982457</v>
       </c>
       <c r="J324">
         <v>6.5</v>
@@ -13455,7 +13455,7 @@
         <v>-8.5182</v>
       </c>
       <c r="I327">
-        <v>0.8065350877192982</v>
+        <v>0.8065350877192983</v>
       </c>
       <c r="J327">
         <v>6.5</v>
@@ -13721,7 +13721,7 @@
         <v>-4.7487</v>
       </c>
       <c r="I334">
-        <v>-0.01714210526315788</v>
+        <v>-0.01714210526315789</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -14139,7 +14139,7 @@
         <v>-8.935499999999999</v>
       </c>
       <c r="I345">
-        <v>-0.403038596491228</v>
+        <v>-0.4030385964912281</v>
       </c>
       <c r="J345">
         <v>6.5</v>
@@ -14405,7 +14405,7 @@
         <v>-5.7369</v>
       </c>
       <c r="I352">
-        <v>0.5323438596491228</v>
+        <v>0.5323438596491229</v>
       </c>
       <c r="J352">
         <v>6.5</v>
@@ -14785,7 +14785,7 @@
         <v>-5.1904</v>
       </c>
       <c r="I362">
-        <v>0.05131228070175438</v>
+        <v>0.05131228070175436</v>
       </c>
       <c r="J362">
         <v>6.5</v>
@@ -14937,7 +14937,7 @@
         <v>-4.4561</v>
       </c>
       <c r="I366">
-        <v>0.5883254385964911</v>
+        <v>0.5883254385964913</v>
       </c>
       <c r="J366">
         <v>6.5</v>
@@ -15051,7 +15051,7 @@
         <v>-7.5056</v>
       </c>
       <c r="I369">
-        <v>0.8824122807017544</v>
+        <v>0.8824122807017545</v>
       </c>
       <c r="J369">
         <v>6.5</v>
@@ -15393,7 +15393,7 @@
         <v>-5.1258</v>
       </c>
       <c r="I378">
-        <v>0.7531894736842104</v>
+        <v>0.7531894736842105</v>
       </c>
       <c r="J378">
         <v>6.5</v>
@@ -16153,7 +16153,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I398">
-        <v>0.8492342105263159</v>
+        <v>0.8492342105263158</v>
       </c>
       <c r="J398">
         <v>6.5</v>
@@ -16343,7 +16343,7 @@
         <v>-25.5842</v>
       </c>
       <c r="I403">
-        <v>0.9268140350877192</v>
+        <v>0.9268140350877193</v>
       </c>
       <c r="J403">
         <v>6.5</v>
@@ -16723,7 +16723,7 @@
         <v>-5.6733</v>
       </c>
       <c r="I413">
-        <v>-0.1435087719298246</v>
+        <v>-0.1435087719298245</v>
       </c>
       <c r="J413">
         <v>6.5</v>
@@ -16875,7 +16875,7 @@
         <v>-6.1057</v>
       </c>
       <c r="I417">
-        <v>0.7022105263157894</v>
+        <v>0.7022105263157895</v>
       </c>
       <c r="J417">
         <v>6.5</v>
@@ -17179,7 +17179,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I425">
-        <v>0.8890823008849557</v>
+        <v>0.8890823008849558</v>
       </c>
       <c r="J425">
         <v>6.5</v>
@@ -17977,7 +17977,7 @@
         <v>-6.6293</v>
       </c>
       <c r="I446">
-        <v>0.9794122807017545</v>
+        <v>0.9794122807017543</v>
       </c>
       <c r="J446">
         <v>6.5</v>
@@ -18015,7 +18015,7 @@
         <v>-6.0852</v>
       </c>
       <c r="I447">
-        <v>0.8567078947368422</v>
+        <v>0.8567078947368421</v>
       </c>
       <c r="J447">
         <v>6.5</v>
@@ -18623,7 +18623,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I463">
-        <v>-0.005909649122807043</v>
+        <v>-0.005909649122807035</v>
       </c>
       <c r="J463">
         <v>6.5</v>
@@ -18661,7 +18661,7 @@
         <v>-4.248</v>
       </c>
       <c r="I464">
-        <v>-0.2478280701754387</v>
+        <v>-0.2478280701754386</v>
       </c>
       <c r="J464">
         <v>6.5</v>
@@ -18889,7 +18889,7 @@
         <v>-4.958</v>
       </c>
       <c r="I470">
-        <v>0.01515087719298249</v>
+        <v>0.01515087719298248</v>
       </c>
       <c r="J470">
         <v>6.5</v>
@@ -19725,7 +19725,7 @@
         <v>-5.1068</v>
       </c>
       <c r="I492">
-        <v>0.09810263157894737</v>
+        <v>0.09810263157894739</v>
       </c>
       <c r="J492">
         <v>6.5</v>
@@ -19953,7 +19953,7 @@
         <v>-5.9807</v>
       </c>
       <c r="I498">
-        <v>0.9388535087719299</v>
+        <v>0.9388535087719297</v>
       </c>
       <c r="J498">
         <v>6.5</v>
@@ -20257,7 +20257,7 @@
         <v>-6.9126</v>
       </c>
       <c r="I506">
-        <v>-0.007017543859649098</v>
+        <v>-0.007017543859649127</v>
       </c>
       <c r="J506">
         <v>6.5</v>
@@ -20865,7 +20865,7 @@
         <v>-5.2765</v>
       </c>
       <c r="I522">
-        <v>-0.04416403508771931</v>
+        <v>-0.04416403508771927</v>
       </c>
       <c r="J522">
         <v>6.5</v>
@@ -21587,7 +21587,7 @@
         <v>-7.8784</v>
       </c>
       <c r="I541">
-        <v>-0.1674350877192983</v>
+        <v>-0.1674350877192982</v>
       </c>
       <c r="J541">
         <v>6.5</v>
@@ -22005,7 +22005,7 @@
         <v>-5.5816</v>
       </c>
       <c r="I552">
-        <v>0.09724473684210529</v>
+        <v>0.09724473684210526</v>
       </c>
       <c r="J552">
         <v>6.5</v>
@@ -22157,7 +22157,7 @@
         <v>-5.7724</v>
       </c>
       <c r="I556">
-        <v>0.1150850877192983</v>
+        <v>0.1150850877192982</v>
       </c>
       <c r="J556">
         <v>6.5</v>
@@ -22499,7 +22499,7 @@
         <v>-8.0747</v>
       </c>
       <c r="I565">
-        <v>0.5883105263157894</v>
+        <v>0.5883105263157895</v>
       </c>
       <c r="J565">
         <v>6.5</v>
@@ -24209,7 +24209,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I610">
-        <v>-0.05798157894736837</v>
+        <v>-0.05798157894736838</v>
       </c>
       <c r="J610">
         <v>6.5</v>
@@ -24285,7 +24285,7 @@
         <v>-5.6399</v>
       </c>
       <c r="I612">
-        <v>0.9184254385964913</v>
+        <v>0.9184254385964912</v>
       </c>
       <c r="J612">
         <v>6.5</v>
@@ -24437,7 +24437,7 @@
         <v>-5.9518</v>
       </c>
       <c r="I616">
-        <v>0.5545859649122807</v>
+        <v>0.5545859649122806</v>
       </c>
       <c r="J616">
         <v>6.5</v>
@@ -24589,7 +24589,7 @@
         <v>-4.9069</v>
       </c>
       <c r="I620">
-        <v>0.9718342105263158</v>
+        <v>0.9718342105263157</v>
       </c>
       <c r="J620">
         <v>6.5</v>
@@ -24855,7 +24855,7 @@
         <v>-6.4458</v>
       </c>
       <c r="I627">
-        <v>0.7589105263157895</v>
+        <v>0.7589105263157896</v>
       </c>
       <c r="J627">
         <v>6.5</v>
@@ -24893,7 +24893,7 @@
         <v>-4.9452</v>
       </c>
       <c r="I628">
-        <v>0.4920342105263158</v>
+        <v>0.4920342105263157</v>
       </c>
       <c r="J628">
         <v>6.5</v>
@@ -25083,7 +25083,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I633">
-        <v>0.04088859649122808</v>
+        <v>0.04088859649122805</v>
       </c>
       <c r="J633">
         <v>6.5</v>
@@ -25159,7 +25159,7 @@
         <v>-6.532</v>
       </c>
       <c r="I635">
-        <v>0.01685877192982452</v>
+        <v>0.01685877192982456</v>
       </c>
       <c r="J635">
         <v>6.5</v>
@@ -25197,7 +25197,7 @@
         <v>-8.580500000000001</v>
       </c>
       <c r="I636">
-        <v>-0.4958578947368421</v>
+        <v>-0.4958578947368422</v>
       </c>
       <c r="J636">
         <v>6.5</v>
@@ -25311,7 +25311,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I639">
-        <v>0.3845070175438596</v>
+        <v>0.3845070175438597</v>
       </c>
       <c r="J639">
         <v>6.5</v>
@@ -25729,7 +25729,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I650">
-        <v>-0.2874561403508772</v>
+        <v>-0.2874561403508771</v>
       </c>
       <c r="J650">
         <v>6.5</v>
@@ -26147,7 +26147,7 @@
         <v>-5.7948</v>
       </c>
       <c r="I661">
-        <v>-0.07977982456140351</v>
+        <v>-0.07977982456140346</v>
       </c>
       <c r="J661">
         <v>6.5</v>
@@ -26489,7 +26489,7 @@
         <v>-7.7299</v>
       </c>
       <c r="I670">
-        <v>0.3379807017543859</v>
+        <v>0.337980701754386</v>
       </c>
       <c r="J670">
         <v>6.5</v>
@@ -26565,7 +26565,7 @@
         <v>-8.907500000000001</v>
       </c>
       <c r="I672">
-        <v>0.05063859649122808</v>
+        <v>0.05063859649122809</v>
       </c>
       <c r="J672">
         <v>6.5</v>
@@ -27439,7 +27439,7 @@
         <v>-5.7765</v>
       </c>
       <c r="I695">
-        <v>2.46108947368421</v>
+        <v>2.461089473684211</v>
       </c>
       <c r="J695">
         <v>6.5</v>
@@ -27743,7 +27743,7 @@
         <v>-8.2332</v>
       </c>
       <c r="I703">
-        <v>-0.2289008771929825</v>
+        <v>-0.2289008771929824</v>
       </c>
       <c r="J703">
         <v>6.5</v>
@@ -28275,7 +28275,7 @@
         <v>-5.1711</v>
       </c>
       <c r="I717">
-        <v>0.7814701754385965</v>
+        <v>0.7814701754385964</v>
       </c>
       <c r="J717">
         <v>6.5</v>
@@ -28465,7 +28465,7 @@
         <v>-7.076</v>
       </c>
       <c r="I722">
-        <v>0.7335359649122807</v>
+        <v>0.7335359649122808</v>
       </c>
       <c r="J722">
         <v>6.5</v>
@@ -28503,7 +28503,7 @@
         <v>-6.4442</v>
       </c>
       <c r="I723">
-        <v>0.7272859649122806</v>
+        <v>0.7272859649122807</v>
       </c>
       <c r="J723">
         <v>6.5</v>
@@ -28693,7 +28693,7 @@
         <v>-4.1714</v>
       </c>
       <c r="I728">
-        <v>0.03119473684210523</v>
+        <v>0.03119473684210524</v>
       </c>
       <c r="J728">
         <v>6.5</v>
@@ -29491,7 +29491,7 @@
         <v>-6.2194</v>
       </c>
       <c r="I749">
-        <v>0.4190657894736842</v>
+        <v>0.4190657894736843</v>
       </c>
       <c r="J749">
         <v>6.5</v>
@@ -29567,7 +29567,7 @@
         <v>-6.5425</v>
       </c>
       <c r="I751">
-        <v>0.376430701754386</v>
+        <v>0.3764307017543859</v>
       </c>
       <c r="J751">
         <v>6.5</v>
@@ -31201,7 +31201,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I794">
-        <v>0.4163964912280702</v>
+        <v>0.4163964912280703</v>
       </c>
       <c r="J794">
         <v>6.5</v>
@@ -31581,7 +31581,7 @@
         <v>-7.0178</v>
       </c>
       <c r="I804">
-        <v>0.3055201754385964</v>
+        <v>0.3055201754385965</v>
       </c>
       <c r="J804">
         <v>6.5</v>
@@ -32075,7 +32075,7 @@
         <v>-5.9799</v>
       </c>
       <c r="I817">
-        <v>0.823928947368421</v>
+        <v>0.8239289473684211</v>
       </c>
       <c r="J817">
         <v>6.5</v>
@@ -32113,7 +32113,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I818">
-        <v>-0.05369473684210526</v>
+        <v>-0.05369473684210529</v>
       </c>
       <c r="J818">
         <v>6.5</v>
@@ -32189,7 +32189,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I820">
-        <v>0.09694385964912279</v>
+        <v>0.09694385964912282</v>
       </c>
       <c r="J820">
         <v>6.5</v>
@@ -33177,7 +33177,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I846">
-        <v>-0.08320087719298247</v>
+        <v>-0.08320087719298248</v>
       </c>
       <c r="J846">
         <v>6.5</v>
@@ -33405,7 +33405,7 @@
         <v>-5.9691</v>
       </c>
       <c r="I852">
-        <v>-0.09673684210526312</v>
+        <v>-0.09673684210526315</v>
       </c>
       <c r="J852">
         <v>6.5</v>
@@ -33595,7 +33595,7 @@
         <v>-5.1365</v>
       </c>
       <c r="I857">
-        <v>0.3506315789473683</v>
+        <v>0.3506315789473684</v>
       </c>
       <c r="J857">
         <v>6.5</v>
@@ -33975,7 +33975,7 @@
         <v>-5.9705</v>
       </c>
       <c r="I867">
-        <v>0.8947973684210525</v>
+        <v>0.8947973684210526</v>
       </c>
       <c r="J867">
         <v>6.5</v>
@@ -34127,7 +34127,7 @@
         <v>-5.7904</v>
       </c>
       <c r="I871">
-        <v>-0.01008245614035088</v>
+        <v>-0.01008245614035089</v>
       </c>
       <c r="J871">
         <v>6.5</v>
@@ -35495,7 +35495,7 @@
         <v>-5.3294</v>
       </c>
       <c r="I907">
-        <v>1.266428070175439</v>
+        <v>1.266428070175438</v>
       </c>
       <c r="J907">
         <v>6.5</v>
@@ -36255,7 +36255,7 @@
         <v>-6.6449</v>
       </c>
       <c r="I927">
-        <v>0.5105999999999999</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J927">
         <v>6.5</v>
@@ -36483,7 +36483,7 @@
         <v>-6.8076</v>
       </c>
       <c r="I933">
-        <v>0.07269473684210527</v>
+        <v>0.07269473684210526</v>
       </c>
       <c r="J933">
         <v>6.5</v>
@@ -37091,7 +37091,7 @@
         <v>-5.5354</v>
       </c>
       <c r="I949">
-        <v>0.266107894736842</v>
+        <v>0.2661078947368421</v>
       </c>
       <c r="J949">
         <v>6.5</v>
@@ -37129,7 +37129,7 @@
         <v>-6.2272</v>
       </c>
       <c r="I950">
-        <v>0.04605309734513276</v>
+        <v>0.04605309734513275</v>
       </c>
       <c r="J950">
         <v>6.5</v>
@@ -37737,7 +37737,7 @@
         <v>-8.7384</v>
       </c>
       <c r="I966">
-        <v>0.03935526315789473</v>
+        <v>0.03935526315789474</v>
       </c>
       <c r="J966">
         <v>6.5</v>
@@ -38649,7 +38649,7 @@
         <v>-5.9258</v>
       </c>
       <c r="I990">
-        <v>0.6400684210526317</v>
+        <v>0.6400684210526315</v>
       </c>
       <c r="J990">
         <v>6.5</v>
@@ -39675,7 +39675,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I1017">
-        <v>0.04960877192982453</v>
+        <v>0.04960877192982454</v>
       </c>
       <c r="J1017">
         <v>6.5</v>
@@ -39865,7 +39865,7 @@
         <v>-7.706</v>
       </c>
       <c r="I1022">
-        <v>-0.01646666666666671</v>
+        <v>-0.01646666666666668</v>
       </c>
       <c r="J1022">
         <v>6.5</v>
@@ -39979,7 +39979,7 @@
         <v>-6.4182</v>
       </c>
       <c r="I1025">
-        <v>0.7823140350877192</v>
+        <v>0.7823140350877194</v>
       </c>
       <c r="J1025">
         <v>6.5</v>
@@ -40207,7 +40207,7 @@
         <v>-7.3081</v>
       </c>
       <c r="I1031">
-        <v>0.06260964912280705</v>
+        <v>0.06260964912280706</v>
       </c>
       <c r="J1031">
         <v>6.5</v>
@@ -40283,7 +40283,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I1033">
-        <v>0.01259649122807015</v>
+        <v>0.01259649122807016</v>
       </c>
       <c r="J1033">
         <v>6.5</v>

--- a/resources/M673/spc_sheet_oos_detail.xlsx
+++ b/resources/M673/spc_sheet_oos_detail.xlsx
@@ -1371,7 +1371,7 @@
         <v>-3.2048</v>
       </c>
       <c r="I9">
-        <v>0.1313833333333334</v>
+        <v>0.1313833333333333</v>
       </c>
       <c r="J9">
         <v>6.5</v>
@@ -1789,7 +1789,7 @@
         <v>-3.2936</v>
       </c>
       <c r="I20">
-        <v>0.7082675438596491</v>
+        <v>0.7082675438596492</v>
       </c>
       <c r="J20">
         <v>6.5</v>
@@ -2017,7 +2017,7 @@
         <v>-7.3392</v>
       </c>
       <c r="I26">
-        <v>-0.05725964912280702</v>
+        <v>-0.057259649122807</v>
       </c>
       <c r="J26">
         <v>6.5</v>
@@ -2549,7 +2549,7 @@
         <v>-6.8108</v>
       </c>
       <c r="I40">
-        <v>-0.07766140350877193</v>
+        <v>-0.07766140350877195</v>
       </c>
       <c r="J40">
         <v>6.5</v>
@@ -2929,7 +2929,7 @@
         <v>-5.1686</v>
       </c>
       <c r="I50">
-        <v>0.06831403508771933</v>
+        <v>0.06831403508771931</v>
       </c>
       <c r="J50">
         <v>6.5</v>
@@ -3081,7 +3081,7 @@
         <v>-7.5421</v>
       </c>
       <c r="I54">
-        <v>-8.7719298245171E-06</v>
+        <v>-8.771929824524404E-06</v>
       </c>
       <c r="J54">
         <v>6.5</v>
@@ -3651,7 +3651,7 @@
         <v>-5.3978</v>
       </c>
       <c r="I69">
-        <v>0.7009289473684209</v>
+        <v>0.700928947368421</v>
       </c>
       <c r="J69">
         <v>6.5</v>
@@ -3803,7 +3803,7 @@
         <v>-6.1023</v>
       </c>
       <c r="I73">
-        <v>-0.1370429824561404</v>
+        <v>-0.1370429824561403</v>
       </c>
       <c r="J73">
         <v>6.5</v>
@@ -3917,7 +3917,7 @@
         <v>-7.1749</v>
       </c>
       <c r="I76">
-        <v>0.3746035087719299</v>
+        <v>0.3746035087719298</v>
       </c>
       <c r="J76">
         <v>6.5</v>
@@ -4259,7 +4259,7 @@
         <v>-5.5616</v>
       </c>
       <c r="I85">
-        <v>-0.005708771929824567</v>
+        <v>-0.005708771929824523</v>
       </c>
       <c r="J85">
         <v>6.5</v>
@@ -4525,7 +4525,7 @@
         <v>-5.325</v>
       </c>
       <c r="I92">
-        <v>0.06181315789473684</v>
+        <v>0.06181315789473681</v>
       </c>
       <c r="J92">
         <v>6.5</v>
@@ -4563,7 +4563,7 @@
         <v>-5.5639</v>
       </c>
       <c r="I93">
-        <v>0.0316017543859649</v>
+        <v>0.03160175438596492</v>
       </c>
       <c r="J93">
         <v>6.5</v>
@@ -4601,7 +4601,7 @@
         <v>-4.9943</v>
       </c>
       <c r="I94">
-        <v>0.01033684210526315</v>
+        <v>0.01033684210526314</v>
       </c>
       <c r="J94">
         <v>6.5</v>
@@ -4753,7 +4753,7 @@
         <v>-5.5499</v>
       </c>
       <c r="I98">
-        <v>0.3972052631578947</v>
+        <v>0.3972052631578948</v>
       </c>
       <c r="J98">
         <v>6.5</v>
@@ -4905,7 +4905,7 @@
         <v>-5.5111</v>
       </c>
       <c r="I102">
-        <v>0.9372763157894738</v>
+        <v>0.9372763157894736</v>
       </c>
       <c r="J102">
         <v>6.5</v>
@@ -5019,7 +5019,7 @@
         <v>-5.7006</v>
       </c>
       <c r="I105">
-        <v>-0.2644166666666666</v>
+        <v>-0.2644166666666667</v>
       </c>
       <c r="J105">
         <v>6.5</v>
@@ -5057,7 +5057,7 @@
         <v>-3.7504</v>
       </c>
       <c r="I106">
-        <v>1.033949122807017</v>
+        <v>1.033949122807018</v>
       </c>
       <c r="J106">
         <v>6.5</v>
@@ -5475,7 +5475,7 @@
         <v>-4.7549</v>
       </c>
       <c r="I117">
-        <v>-0.0955973684210526</v>
+        <v>-0.09559736842105261</v>
       </c>
       <c r="J117">
         <v>6.5</v>
@@ -5551,7 +5551,7 @@
         <v>-4.9268</v>
       </c>
       <c r="I119">
-        <v>0.1207350877192983</v>
+        <v>0.1207350877192982</v>
       </c>
       <c r="J119">
         <v>6.5</v>
@@ -5817,7 +5817,7 @@
         <v>-4.8548</v>
       </c>
       <c r="I126">
-        <v>-0.02022920353982301</v>
+        <v>-0.02022920353982299</v>
       </c>
       <c r="J126">
         <v>6.5</v>
@@ -6045,7 +6045,7 @@
         <v>-4.7021</v>
       </c>
       <c r="I132">
-        <v>-0.04365350877192985</v>
+        <v>-0.04365350877192986</v>
       </c>
       <c r="J132">
         <v>6.5</v>
@@ -6121,7 +6121,7 @@
         <v>-5.4098</v>
       </c>
       <c r="I134">
-        <v>-0.2065377192982457</v>
+        <v>-0.2065377192982456</v>
       </c>
       <c r="J134">
         <v>6.5</v>
@@ -6159,7 +6159,7 @@
         <v>-5.6503</v>
       </c>
       <c r="I135">
-        <v>0.4333245614035087</v>
+        <v>0.4333245614035088</v>
       </c>
       <c r="J135">
         <v>6.5</v>
@@ -6197,7 +6197,7 @@
         <v>-4.3533</v>
       </c>
       <c r="I136">
-        <v>0.7331824561403508</v>
+        <v>0.7331824561403509</v>
       </c>
       <c r="J136">
         <v>6.5</v>
@@ -6235,7 +6235,7 @@
         <v>-6.3804</v>
       </c>
       <c r="I137">
-        <v>0.01184473684210523</v>
+        <v>0.01184473684210524</v>
       </c>
       <c r="J137">
         <v>6.5</v>
@@ -6273,7 +6273,7 @@
         <v>-6.1406</v>
       </c>
       <c r="I138">
-        <v>-0.1075850877192983</v>
+        <v>-0.1075850877192982</v>
       </c>
       <c r="J138">
         <v>6.5</v>
@@ -6349,7 +6349,7 @@
         <v>-5.4954</v>
       </c>
       <c r="I140">
-        <v>-0.07092123893805304</v>
+        <v>-0.07092123893805306</v>
       </c>
       <c r="J140">
         <v>6.5</v>
@@ -6653,7 +6653,7 @@
         <v>-4.2556</v>
       </c>
       <c r="I148">
-        <v>0.5377736842105264</v>
+        <v>0.5377736842105263</v>
       </c>
       <c r="J148">
         <v>6.5</v>
@@ -6767,7 +6767,7 @@
         <v>-5.5488</v>
       </c>
       <c r="I151">
-        <v>-0.09169736842105258</v>
+        <v>-0.09169736842105267</v>
       </c>
       <c r="J151">
         <v>6.5</v>
@@ -7071,7 +7071,7 @@
         <v>-6.2914</v>
       </c>
       <c r="I159">
-        <v>0.03470701754385963</v>
+        <v>0.0347070175438596</v>
       </c>
       <c r="J159">
         <v>6.5</v>
@@ -7147,7 +7147,7 @@
         <v>-5.9529</v>
       </c>
       <c r="I161">
-        <v>-0.4892543859649123</v>
+        <v>-0.4892543859649122</v>
       </c>
       <c r="J161">
         <v>6.5</v>
@@ -7299,7 +7299,7 @@
         <v>-4.6257</v>
       </c>
       <c r="I165">
-        <v>0.1766570175438596</v>
+        <v>0.1766570175438597</v>
       </c>
       <c r="J165">
         <v>6.5</v>
@@ -7337,7 +7337,7 @@
         <v>-5.0848</v>
       </c>
       <c r="I166">
-        <v>-0.5323552631578948</v>
+        <v>-0.5323552631578947</v>
       </c>
       <c r="J166">
         <v>6.5</v>
@@ -7489,7 +7489,7 @@
         <v>-4.7969</v>
       </c>
       <c r="I170">
-        <v>0.2609666666666666</v>
+        <v>0.2609666666666667</v>
       </c>
       <c r="J170">
         <v>6.5</v>
@@ -7527,7 +7527,7 @@
         <v>-4.4651</v>
       </c>
       <c r="I171">
-        <v>-0.04652807017543861</v>
+        <v>-0.04652807017543858</v>
       </c>
       <c r="J171">
         <v>6.5</v>
@@ -7831,7 +7831,7 @@
         <v>-8.343400000000001</v>
       </c>
       <c r="I179">
-        <v>-0.8040798245614035</v>
+        <v>-0.8040798245614036</v>
       </c>
       <c r="J179">
         <v>6.5</v>
@@ -7983,7 +7983,7 @@
         <v>-6.4771</v>
       </c>
       <c r="I183">
-        <v>-0.3391140350877193</v>
+        <v>-0.3391140350877194</v>
       </c>
       <c r="J183">
         <v>6.5</v>
@@ -8021,7 +8021,7 @@
         <v>-8.4955</v>
       </c>
       <c r="I184">
-        <v>0.5397631578947368</v>
+        <v>0.5397631578947369</v>
       </c>
       <c r="J184">
         <v>6.5</v>
@@ -8059,7 +8059,7 @@
         <v>-6.9804</v>
       </c>
       <c r="I185">
-        <v>-0.008550000000000035</v>
+        <v>-0.008550000000000037</v>
       </c>
       <c r="J185">
         <v>6.5</v>
@@ -8173,7 +8173,7 @@
         <v>-5.5468</v>
       </c>
       <c r="I188">
-        <v>-0.05237192982456141</v>
+        <v>-0.05237192982456142</v>
       </c>
       <c r="J188">
         <v>6.5</v>
@@ -8325,7 +8325,7 @@
         <v>-4.7361</v>
       </c>
       <c r="I192">
-        <v>0.3821929824561403</v>
+        <v>0.3821929824561404</v>
       </c>
       <c r="J192">
         <v>6.5</v>
@@ -8363,7 +8363,7 @@
         <v>-6.5935</v>
       </c>
       <c r="I193">
-        <v>-0.2784456140350877</v>
+        <v>-0.2784456140350878</v>
       </c>
       <c r="J193">
         <v>6.5</v>
@@ -8401,7 +8401,7 @@
         <v>-5.5309</v>
       </c>
       <c r="I194">
-        <v>-0.5048745614035087</v>
+        <v>-0.5048745614035088</v>
       </c>
       <c r="J194">
         <v>6.5</v>
@@ -8629,7 +8629,7 @@
         <v>-4.3684</v>
       </c>
       <c r="I200">
-        <v>0.958109649122807</v>
+        <v>0.9581096491228069</v>
       </c>
       <c r="J200">
         <v>6.5</v>
@@ -8667,7 +8667,7 @@
         <v>-5.7729</v>
       </c>
       <c r="I201">
-        <v>0.2905122807017543</v>
+        <v>0.2905122807017544</v>
       </c>
       <c r="J201">
         <v>6.5</v>
@@ -8743,7 +8743,7 @@
         <v>-4.8514</v>
       </c>
       <c r="I203">
-        <v>1.477787719298246</v>
+        <v>1.477787719298245</v>
       </c>
       <c r="J203">
         <v>6.5</v>
@@ -8857,7 +8857,7 @@
         <v>-5.8919</v>
       </c>
       <c r="I206">
-        <v>-0.006774561403508753</v>
+        <v>-0.006774561403508795</v>
       </c>
       <c r="J206">
         <v>6.5</v>
@@ -8933,7 +8933,7 @@
         <v>-5.2636</v>
       </c>
       <c r="I208">
-        <v>-0.09407280701754384</v>
+        <v>-0.09407280701754382</v>
       </c>
       <c r="J208">
         <v>6.5</v>
@@ -9161,7 +9161,7 @@
         <v>-6.3484</v>
       </c>
       <c r="I214">
-        <v>0.0961122807017544</v>
+        <v>0.09611228070175443</v>
       </c>
       <c r="J214">
         <v>6.5</v>
@@ -9275,7 +9275,7 @@
         <v>-6.421</v>
       </c>
       <c r="I217">
-        <v>0.7688903508771929</v>
+        <v>0.768890350877193</v>
       </c>
       <c r="J217">
         <v>6.5</v>
@@ -9959,7 +9959,7 @@
         <v>-7.0988</v>
       </c>
       <c r="I235">
-        <v>-0.02176052631578946</v>
+        <v>-0.0217605263157895</v>
       </c>
       <c r="J235">
         <v>6.5</v>
@@ -10263,7 +10263,7 @@
         <v>-6.3915</v>
       </c>
       <c r="I243">
-        <v>0.3867263157894737</v>
+        <v>0.3867263157894736</v>
       </c>
       <c r="J243">
         <v>6.5</v>
@@ -10301,7 +10301,7 @@
         <v>-7.8256</v>
       </c>
       <c r="I244">
-        <v>0.038790350877193</v>
+        <v>0.03879035087719299</v>
       </c>
       <c r="J244">
         <v>6.5</v>
@@ -10643,7 +10643,7 @@
         <v>-8.3277</v>
       </c>
       <c r="I253">
-        <v>-0.9198491228070176</v>
+        <v>-0.9198491228070175</v>
       </c>
       <c r="J253">
         <v>6.5</v>
@@ -10757,7 +10757,7 @@
         <v>-4.0971</v>
       </c>
       <c r="I256">
-        <v>0.597848245614035</v>
+        <v>0.5978482456140352</v>
       </c>
       <c r="J256">
         <v>6.5</v>
@@ -11213,7 +11213,7 @@
         <v>-7.0616</v>
       </c>
       <c r="I268">
-        <v>0.3301157894736841</v>
+        <v>0.3301157894736843</v>
       </c>
       <c r="J268">
         <v>6.5</v>
@@ -11479,7 +11479,7 @@
         <v>-9.9345</v>
       </c>
       <c r="I275">
-        <v>-0.09860000000000002</v>
+        <v>-0.09860000000000006</v>
       </c>
       <c r="J275">
         <v>6.5</v>
@@ -11821,7 +11821,7 @@
         <v>-5.579</v>
       </c>
       <c r="I284">
-        <v>0.03944473684210526</v>
+        <v>0.03944473684210527</v>
       </c>
       <c r="J284">
         <v>6.5</v>
@@ -12467,7 +12467,7 @@
         <v>-7.4805</v>
       </c>
       <c r="I301">
-        <v>0.08061228070175437</v>
+        <v>0.08061228070175436</v>
       </c>
       <c r="J301">
         <v>6.5</v>
@@ -12695,7 +12695,7 @@
         <v>-8.475300000000001</v>
       </c>
       <c r="I307">
-        <v>0.6196201754385964</v>
+        <v>0.6196201754385965</v>
       </c>
       <c r="J307">
         <v>6.5</v>
@@ -12809,7 +12809,7 @@
         <v>-5.6215</v>
       </c>
       <c r="I310">
-        <v>0.9777149122807017</v>
+        <v>0.9777149122807018</v>
       </c>
       <c r="J310">
         <v>6.5</v>
@@ -13075,7 +13075,7 @@
         <v>-7.9728</v>
       </c>
       <c r="I317">
-        <v>0.8969166666666666</v>
+        <v>0.8969166666666667</v>
       </c>
       <c r="J317">
         <v>6.5</v>
@@ -13341,7 +13341,7 @@
         <v>-5.1407</v>
       </c>
       <c r="I324">
-        <v>0.2866377192982457</v>
+        <v>0.2866377192982456</v>
       </c>
       <c r="J324">
         <v>6.5</v>
@@ -13531,7 +13531,7 @@
         <v>-10.5468</v>
       </c>
       <c r="I329">
-        <v>-0.06476842105263157</v>
+        <v>-0.06476842105263156</v>
       </c>
       <c r="J329">
         <v>6.5</v>
@@ -13645,7 +13645,7 @@
         <v>-4.5464</v>
       </c>
       <c r="I332">
-        <v>0.7982622807017544</v>
+        <v>0.7982622807017543</v>
       </c>
       <c r="J332">
         <v>6.5</v>
@@ -13721,7 +13721,7 @@
         <v>-4.7487</v>
       </c>
       <c r="I334">
-        <v>-0.01714210526315789</v>
+        <v>-0.01714210526315788</v>
       </c>
       <c r="J334">
         <v>6.5</v>
@@ -14139,7 +14139,7 @@
         <v>-8.935499999999999</v>
       </c>
       <c r="I345">
-        <v>-0.4030385964912281</v>
+        <v>-0.403038596491228</v>
       </c>
       <c r="J345">
         <v>6.5</v>
@@ -14785,7 +14785,7 @@
         <v>-5.1904</v>
       </c>
       <c r="I362">
-        <v>0.05131228070175436</v>
+        <v>0.05131228070175434</v>
       </c>
       <c r="J362">
         <v>6.5</v>
@@ -15051,7 +15051,7 @@
         <v>-7.5056</v>
       </c>
       <c r="I369">
-        <v>0.8824122807017545</v>
+        <v>0.8824122807017544</v>
       </c>
       <c r="J369">
         <v>6.5</v>
@@ -15849,7 +15849,7 @@
         <v>-4.5944</v>
       </c>
       <c r="I390">
-        <v>0.7309088495575221</v>
+        <v>0.7309088495575222</v>
       </c>
       <c r="J390">
         <v>6.5</v>
@@ -16153,7 +16153,7 @@
         <v>-5.6271</v>
       </c>
       <c r="I398">
-        <v>0.8492342105263158</v>
+        <v>0.8492342105263159</v>
       </c>
       <c r="J398">
         <v>6.5</v>
@@ -16229,7 +16229,7 @@
         <v>-5.3412</v>
       </c>
       <c r="I400">
-        <v>0.3154666666666666</v>
+        <v>0.3154666666666667</v>
       </c>
       <c r="J400">
         <v>6.5</v>
@@ -16723,7 +16723,7 @@
         <v>-5.6733</v>
       </c>
       <c r="I413">
-        <v>-0.1435087719298245</v>
+        <v>-0.1435087719298246</v>
       </c>
       <c r="J413">
         <v>6.5</v>
@@ -17179,7 +17179,7 @@
         <v>-14.0222</v>
       </c>
       <c r="I425">
-        <v>0.8890823008849558</v>
+        <v>0.8890823008849557</v>
       </c>
       <c r="J425">
         <v>6.5</v>
@@ -17977,7 +17977,7 @@
         <v>-6.6293</v>
       </c>
       <c r="I446">
-        <v>0.9794122807017543</v>
+        <v>0.9794122807017545</v>
       </c>
       <c r="J446">
         <v>6.5</v>
@@ -18319,7 +18319,7 @@
         <v>-8.1053</v>
       </c>
       <c r="I455">
-        <v>-0.1222131578947368</v>
+        <v>-0.1222131578947369</v>
       </c>
       <c r="J455">
         <v>6.5</v>
@@ -18623,7 +18623,7 @@
         <v>-7.2617</v>
       </c>
       <c r="I463">
-        <v>-0.005909649122807035</v>
+        <v>-0.005909649122807038</v>
       </c>
       <c r="J463">
         <v>6.5</v>
@@ -18889,7 +18889,7 @@
         <v>-4.958</v>
       </c>
       <c r="I470">
-        <v>0.01515087719298248</v>
+        <v>0.01515087719298249</v>
       </c>
       <c r="J470">
         <v>6.5</v>
@@ -19497,7 +19497,7 @@
         <v>-5.0702</v>
       </c>
       <c r="I486">
-        <v>0.412380701754386</v>
+        <v>0.4123807017543859</v>
       </c>
       <c r="J486">
         <v>6.5</v>
@@ -19725,7 +19725,7 @@
         <v>-5.1068</v>
       </c>
       <c r="I492">
-        <v>0.09810263157894739</v>
+        <v>0.09810263157894737</v>
       </c>
       <c r="J492">
         <v>6.5</v>
@@ -20257,7 +20257,7 @@
         <v>-6.9126</v>
       </c>
       <c r="I506">
-        <v>-0.007017543859649127</v>
+        <v>-0.007017543859649141</v>
       </c>
       <c r="J506">
         <v>6.5</v>
@@ -21093,7 +21093,7 @@
         <v>-5.7272</v>
       </c>
       <c r="I528">
-        <v>-0.1781403508771931</v>
+        <v>-0.178140350877193</v>
       </c>
       <c r="J528">
         <v>6.5</v>
@@ -21397,7 +21397,7 @@
         <v>-5.1151</v>
       </c>
       <c r="I536">
-        <v>0.0915333333333333</v>
+        <v>0.09153333333333333</v>
       </c>
       <c r="J536">
         <v>6.5</v>
@@ -21587,7 +21587,7 @@
         <v>-7.8784</v>
       </c>
       <c r="I541">
-        <v>-0.1674350877192982</v>
+        <v>-0.1674350877192983</v>
       </c>
       <c r="J541">
         <v>6.5</v>
@@ -21815,7 +21815,7 @@
         <v>-6.3641</v>
       </c>
       <c r="I547">
-        <v>0.8495912280701755</v>
+        <v>0.8495912280701754</v>
       </c>
       <c r="J547">
         <v>6.5</v>
@@ -22499,7 +22499,7 @@
         <v>-8.0747</v>
       </c>
       <c r="I565">
-        <v>0.5883105263157895</v>
+        <v>0.5883105263157894</v>
       </c>
       <c r="J565">
         <v>6.5</v>
@@ -23487,7 +23487,7 @@
         <v>-6.9653</v>
       </c>
       <c r="I591">
-        <v>-0.02084210526315791</v>
+        <v>-0.02084210526315789</v>
       </c>
       <c r="J591">
         <v>6.5</v>
@@ -24057,7 +24057,7 @@
         <v>-4.9538</v>
       </c>
       <c r="I606">
-        <v>0.6148710526315789</v>
+        <v>0.614871052631579</v>
       </c>
       <c r="J606">
         <v>6.5</v>
@@ -24209,7 +24209,7 @@
         <v>-6.1278</v>
       </c>
       <c r="I610">
-        <v>-0.05798157894736838</v>
+        <v>-0.05798157894736841</v>
       </c>
       <c r="J610">
         <v>6.5</v>
@@ -24285,7 +24285,7 @@
         <v>-5.6399</v>
       </c>
       <c r="I612">
-        <v>0.9184254385964912</v>
+        <v>0.9184254385964913</v>
       </c>
       <c r="J612">
         <v>6.5</v>
@@ -24437,7 +24437,7 @@
         <v>-5.9518</v>
       </c>
       <c r="I616">
-        <v>0.5545859649122806</v>
+        <v>0.5545859649122807</v>
       </c>
       <c r="J616">
         <v>6.5</v>
@@ -24589,7 +24589,7 @@
         <v>-4.9069</v>
       </c>
       <c r="I620">
-        <v>0.9718342105263157</v>
+        <v>0.9718342105263158</v>
       </c>
       <c r="J620">
         <v>6.5</v>
@@ -24855,7 +24855,7 @@
         <v>-6.4458</v>
       </c>
       <c r="I627">
-        <v>0.7589105263157896</v>
+        <v>0.7589105263157895</v>
       </c>
       <c r="J627">
         <v>6.5</v>
@@ -24893,7 +24893,7 @@
         <v>-4.9452</v>
       </c>
       <c r="I628">
-        <v>0.4920342105263157</v>
+        <v>0.4920342105263158</v>
       </c>
       <c r="J628">
         <v>6.5</v>
@@ -25083,7 +25083,7 @@
         <v>-6.2885</v>
       </c>
       <c r="I633">
-        <v>0.04088859649122805</v>
+        <v>0.04088859649122808</v>
       </c>
       <c r="J633">
         <v>6.5</v>
@@ -25159,7 +25159,7 @@
         <v>-6.532</v>
       </c>
       <c r="I635">
-        <v>0.01685877192982456</v>
+        <v>0.01685877192982454</v>
       </c>
       <c r="J635">
         <v>6.5</v>
@@ -25197,7 +25197,7 @@
         <v>-8.580500000000001</v>
       </c>
       <c r="I636">
-        <v>-0.4958578947368422</v>
+        <v>-0.4958578947368421</v>
       </c>
       <c r="J636">
         <v>6.5</v>
@@ -25311,7 +25311,7 @@
         <v>-6.6815</v>
       </c>
       <c r="I639">
-        <v>0.3845070175438597</v>
+        <v>0.3845070175438596</v>
       </c>
       <c r="J639">
         <v>6.5</v>
@@ -25349,7 +25349,7 @@
         <v>-5.9134</v>
       </c>
       <c r="I640">
-        <v>0.6087508771929824</v>
+        <v>0.6087508771929826</v>
       </c>
       <c r="J640">
         <v>6.5</v>
@@ -25729,7 +25729,7 @@
         <v>-6.1323</v>
       </c>
       <c r="I650">
-        <v>-0.2874561403508771</v>
+        <v>-0.2874561403508772</v>
       </c>
       <c r="J650">
         <v>6.5</v>
@@ -26147,7 +26147,7 @@
         <v>-5.7948</v>
       </c>
       <c r="I661">
-        <v>-0.07977982456140346</v>
+        <v>-0.07977982456140348</v>
       </c>
       <c r="J661">
         <v>6.5</v>
@@ -26755,7 +26755,7 @@
         <v>-9.031000000000001</v>
       </c>
       <c r="I677">
-        <v>-0.8340043859649122</v>
+        <v>-0.8340043859649123</v>
       </c>
       <c r="J677">
         <v>6.5</v>
@@ -27743,7 +27743,7 @@
         <v>-8.2332</v>
       </c>
       <c r="I703">
-        <v>-0.2289008771929824</v>
+        <v>-0.2289008771929825</v>
       </c>
       <c r="J703">
         <v>6.5</v>
@@ -27819,7 +27819,7 @@
         <v>-5.8816</v>
       </c>
       <c r="I705">
-        <v>1.095228070175439</v>
+        <v>1.095228070175438</v>
       </c>
       <c r="J705">
         <v>6.5</v>
@@ -28275,7 +28275,7 @@
         <v>-5.1711</v>
       </c>
       <c r="I717">
-        <v>0.7814701754385964</v>
+        <v>0.7814701754385965</v>
       </c>
       <c r="J717">
         <v>6.5</v>
@@ -28693,7 +28693,7 @@
         <v>-4.1714</v>
       </c>
       <c r="I728">
-        <v>0.03119473684210524</v>
+        <v>0.03119473684210525</v>
       </c>
       <c r="J728">
         <v>6.5</v>
@@ -29111,7 +29111,7 @@
         <v>-5.2556</v>
       </c>
       <c r="I739">
-        <v>0.07302192982456139</v>
+        <v>0.07302192982456138</v>
       </c>
       <c r="J739">
         <v>6.5</v>
@@ -29225,7 +29225,7 @@
         <v>-6.6624</v>
       </c>
       <c r="I742">
-        <v>0.244983185840708</v>
+        <v>0.2449831858407079</v>
       </c>
       <c r="J742">
         <v>6.5</v>
@@ -29567,7 +29567,7 @@
         <v>-6.5425</v>
       </c>
       <c r="I751">
-        <v>0.3764307017543859</v>
+        <v>0.376430701754386</v>
       </c>
       <c r="J751">
         <v>6.5</v>
@@ -29757,7 +29757,7 @@
         <v>-7.4388</v>
       </c>
       <c r="I756">
-        <v>0.8952345132743362</v>
+        <v>0.8952345132743363</v>
       </c>
       <c r="J756">
         <v>6.5</v>
@@ -31201,7 +31201,7 @@
         <v>-6.5794</v>
       </c>
       <c r="I794">
-        <v>0.4163964912280703</v>
+        <v>0.4163964912280702</v>
       </c>
       <c r="J794">
         <v>6.5</v>
@@ -32075,7 +32075,7 @@
         <v>-5.9799</v>
       </c>
       <c r="I817">
-        <v>0.8239289473684211</v>
+        <v>0.823928947368421</v>
       </c>
       <c r="J817">
         <v>6.5</v>
@@ -32113,7 +32113,7 @@
         <v>-6.3672</v>
       </c>
       <c r="I818">
-        <v>-0.05369473684210529</v>
+        <v>-0.05369473684210526</v>
       </c>
       <c r="J818">
         <v>6.5</v>
@@ -32189,7 +32189,7 @@
         <v>-6.3705</v>
       </c>
       <c r="I820">
-        <v>0.09694385964912282</v>
+        <v>0.09694385964912278</v>
       </c>
       <c r="J820">
         <v>6.5</v>
@@ -33177,7 +33177,7 @@
         <v>-6.6538</v>
       </c>
       <c r="I846">
-        <v>-0.08320087719298248</v>
+        <v>-0.08320087719298247</v>
       </c>
       <c r="J846">
         <v>6.5</v>
@@ -33405,7 +33405,7 @@
         <v>-5.9691</v>
       </c>
       <c r="I852">
-        <v>-0.09673684210526315</v>
+        <v>-0.09673684210526313</v>
       </c>
       <c r="J852">
         <v>6.5</v>
@@ -33481,7 +33481,7 @@
         <v>-6.8676</v>
       </c>
       <c r="I854">
-        <v>-0.05854690265486726</v>
+        <v>-0.05854690265486728</v>
       </c>
       <c r="J854">
         <v>6.5</v>
@@ -34127,7 +34127,7 @@
         <v>-5.7904</v>
       </c>
       <c r="I871">
-        <v>-0.01008245614035089</v>
+        <v>-0.01008245614035087</v>
       </c>
       <c r="J871">
         <v>6.5</v>
@@ -34431,7 +34431,7 @@
         <v>-7.0621</v>
       </c>
       <c r="I879">
-        <v>-0.6554561403508772</v>
+        <v>-0.6554561403508773</v>
       </c>
       <c r="J879">
         <v>6.5</v>
@@ -34773,7 +34773,7 @@
         <v>-5.5022</v>
       </c>
       <c r="I888">
-        <v>0.4009543859649122</v>
+        <v>0.4009543859649123</v>
       </c>
       <c r="J888">
         <v>6.5</v>
@@ -34963,7 +34963,7 @@
         <v>-6.183</v>
       </c>
       <c r="I893">
-        <v>0.7718307017543861</v>
+        <v>0.771830701754386</v>
       </c>
       <c r="J893">
         <v>6.5</v>
@@ -35495,7 +35495,7 @@
         <v>-5.3294</v>
       </c>
       <c r="I907">
-        <v>1.266428070175438</v>
+        <v>1.266428070175439</v>
       </c>
       <c r="J907">
         <v>6.5</v>
@@ -35761,7 +35761,7 @@
         <v>-5.5058</v>
       </c>
       <c r="I914">
-        <v>0.6981254385964912</v>
+        <v>0.6981254385964913</v>
       </c>
       <c r="J914">
         <v>6.5</v>
@@ -36521,7 +36521,7 @@
         <v>-5.8651</v>
       </c>
       <c r="I934">
-        <v>0.09259035087719297</v>
+        <v>0.09259035087719296</v>
       </c>
       <c r="J934">
         <v>6.5</v>
@@ -36711,7 +36711,7 @@
         <v>-5.2237</v>
       </c>
       <c r="I939">
-        <v>0.8830491228070175</v>
+        <v>0.8830491228070176</v>
       </c>
       <c r="J939">
         <v>6.5</v>
@@ -37091,7 +37091,7 @@
         <v>-5.5354</v>
       </c>
       <c r="I949">
-        <v>0.2661078947368421</v>
+        <v>0.266107894736842</v>
       </c>
       <c r="J949">
         <v>6.5</v>
@@ -37129,7 +37129,7 @@
         <v>-6.2272</v>
       </c>
       <c r="I950">
-        <v>0.04605309734513275</v>
+        <v>0.04605309734513276</v>
       </c>
       <c r="J950">
         <v>6.5</v>
@@ -37737,7 +37737,7 @@
         <v>-8.7384</v>
       </c>
       <c r="I966">
-        <v>0.03935526315789474</v>
+        <v>0.03935526315789472</v>
       </c>
       <c r="J966">
         <v>6.5</v>
@@ -39675,7 +39675,7 @@
         <v>-8.6503</v>
       </c>
       <c r="I1017">
-        <v>0.04960877192982454</v>
+        <v>0.04960877192982456</v>
       </c>
       <c r="J1017">
         <v>6.5</v>
@@ -39789,7 +39789,7 @@
         <v>-6.9831</v>
       </c>
       <c r="I1020">
-        <v>0.2537947368421053</v>
+        <v>0.2537947368421052</v>
       </c>
       <c r="J1020">
         <v>6.5</v>
@@ -39865,7 +39865,7 @@
         <v>-7.706</v>
       </c>
       <c r="I1022">
-        <v>-0.01646666666666668</v>
+        <v>-0.01646666666666666</v>
       </c>
       <c r="J1022">
         <v>6.5</v>
@@ -40207,7 +40207,7 @@
         <v>-7.3081</v>
       </c>
       <c r="I1031">
-        <v>0.06260964912280706</v>
+        <v>0.06260964912280703</v>
       </c>
       <c r="J1031">
         <v>6.5</v>
@@ -40283,7 +40283,7 @@
         <v>-5.8034</v>
       </c>
       <c r="I1033">
-        <v>0.01259649122807016</v>
+        <v>0.01259649122807014</v>
       </c>
       <c r="J1033">
         <v>6.5</v>
@@ -40663,7 +40663,7 @@
         <v>-6.3647</v>
       </c>
       <c r="I1043">
-        <v>0.4170070175438597</v>
+        <v>0.4170070175438596</v>
       </c>
       <c r="J1043">
         <v>6.5</v>
@@ -40739,7 +40739,7 @@
         <v>-6.4277</v>
       </c>
       <c r="I1045">
-        <v>0.5621114035087719</v>
+        <v>0.562111403508772</v>
       </c>
       <c r="J1045">
         <v>6.5</v>
